--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B1_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B1_session_analysis.xlsx
@@ -898,7 +898,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -953,7 +953,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1010,7 +1010,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1114,7 +1114,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1213,7 +1213,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1305,7 +1305,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1551,7 +1551,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1961,7 +1961,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -2671,7 +2671,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -2718,7 +2718,7 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -2859,7 +2859,7 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -2953,7 +2953,7 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -3000,7 +3000,7 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -3094,7 +3094,7 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -3141,7 +3141,7 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -3928,7 +3928,7 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -3975,7 +3975,7 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -4069,7 +4069,7 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -4163,7 +4163,7 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -4210,7 +4210,7 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -4304,7 +4304,7 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -4351,7 +4351,7 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -4586,7 +4586,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -5091,7 +5091,7 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
@@ -5138,7 +5138,7 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
@@ -5185,7 +5185,7 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
@@ -5279,7 +5279,7 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
@@ -5373,7 +5373,7 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
@@ -5420,7 +5420,7 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
@@ -5514,7 +5514,7 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
@@ -5561,7 +5561,7 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
@@ -5796,7 +5796,7 @@
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
@@ -6301,7 +6301,7 @@
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
@@ -6348,7 +6348,7 @@
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H113" s="2" t="inlineStr">
@@ -6395,7 +6395,7 @@
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H114" s="2" t="inlineStr">
@@ -6489,7 +6489,7 @@
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr">
@@ -6583,7 +6583,7 @@
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr">
@@ -6630,7 +6630,7 @@
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr">
@@ -6724,7 +6724,7 @@
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H121" s="2" t="inlineStr">
@@ -6771,7 +6771,7 @@
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H122" s="2" t="inlineStr">
@@ -7006,7 +7006,7 @@
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H127" s="2" t="inlineStr">
@@ -7507,7 +7507,7 @@
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H138" s="2" t="inlineStr">
@@ -7554,7 +7554,7 @@
       </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H139" s="2" t="inlineStr">
@@ -7601,7 +7601,7 @@
       </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H140" s="2" t="inlineStr">
@@ -7695,7 +7695,7 @@
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H142" s="2" t="inlineStr">
@@ -7789,7 +7789,7 @@
       </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H144" s="2" t="inlineStr">
@@ -7836,7 +7836,7 @@
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H145" s="2" t="inlineStr">
@@ -7930,7 +7930,7 @@
       </c>
       <c r="G147" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H147" s="2" t="inlineStr">
@@ -7977,7 +7977,7 @@
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H148" s="2" t="inlineStr">
@@ -8212,7 +8212,7 @@
       </c>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H153" s="2" t="inlineStr">
@@ -8717,7 +8717,7 @@
       </c>
       <c r="G164" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H164" s="2" t="inlineStr">
@@ -8858,7 +8858,7 @@
       </c>
       <c r="G167" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H167" s="2" t="inlineStr">
@@ -8999,7 +8999,7 @@
       </c>
       <c r="G170" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H170" s="2" t="inlineStr">
@@ -9187,7 +9187,7 @@
       </c>
       <c r="G174" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H174" s="2" t="inlineStr">
@@ -9970,7 +9970,7 @@
       </c>
       <c r="G191" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H191" s="2" t="inlineStr">
@@ -10111,7 +10111,7 @@
       </c>
       <c r="G194" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H194" s="2" t="inlineStr">
@@ -10252,7 +10252,7 @@
       </c>
       <c r="G197" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H197" s="2" t="inlineStr">
@@ -10440,7 +10440,7 @@
       </c>
       <c r="G201" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H201" s="2" t="inlineStr">
@@ -11223,7 +11223,7 @@
       </c>
       <c r="G218" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H218" s="2" t="inlineStr">
@@ -11364,7 +11364,7 @@
       </c>
       <c r="G221" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H221" s="2" t="inlineStr">
@@ -11505,7 +11505,7 @@
       </c>
       <c r="G224" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H224" s="2" t="inlineStr">
@@ -11693,7 +11693,7 @@
       </c>
       <c r="G228" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H228" s="2" t="inlineStr">
@@ -12472,7 +12472,7 @@
       </c>
       <c r="G245" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H245" s="2" t="inlineStr">
@@ -12613,7 +12613,7 @@
       </c>
       <c r="G248" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H248" s="2" t="inlineStr">
@@ -12754,7 +12754,7 @@
       </c>
       <c r="G251" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H251" s="2" t="inlineStr">
@@ -12942,7 +12942,7 @@
       </c>
       <c r="G255" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H255" s="2" t="inlineStr">
@@ -13725,7 +13725,7 @@
       </c>
       <c r="G272" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H272" s="2" t="inlineStr">
@@ -13866,7 +13866,7 @@
       </c>
       <c r="G275" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H275" s="2" t="inlineStr">
@@ -14007,7 +14007,7 @@
       </c>
       <c r="G278" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H278" s="2" t="inlineStr">
@@ -14195,7 +14195,7 @@
       </c>
       <c r="G282" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H282" s="2" t="inlineStr">
@@ -14978,7 +14978,7 @@
       </c>
       <c r="G299" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H299" s="2" t="inlineStr">
@@ -15119,7 +15119,7 @@
       </c>
       <c r="G302" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H302" s="2" t="inlineStr">
@@ -15260,7 +15260,7 @@
       </c>
       <c r="G305" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H305" s="2" t="inlineStr">
@@ -15448,7 +15448,7 @@
       </c>
       <c r="G309" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H309" s="2" t="inlineStr">

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B1_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B1_session_analysis.xlsx
@@ -898,7 +898,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -953,7 +953,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1010,7 +1010,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1114,7 +1114,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1213,7 +1213,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1305,7 +1305,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1551,7 +1551,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1961,7 +1961,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -2671,7 +2671,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -2718,7 +2718,7 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -2859,7 +2859,7 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -2953,7 +2953,7 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -3000,7 +3000,7 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -3094,7 +3094,7 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -3141,7 +3141,7 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -3928,7 +3928,7 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -3975,7 +3975,7 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -4069,7 +4069,7 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -4163,7 +4163,7 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -4210,7 +4210,7 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -4304,7 +4304,7 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -4351,7 +4351,7 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -4586,7 +4586,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -5091,7 +5091,7 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
@@ -5138,7 +5138,7 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
@@ -5185,7 +5185,7 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
@@ -5279,7 +5279,7 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
@@ -5373,7 +5373,7 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
@@ -5420,7 +5420,7 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
@@ -5514,7 +5514,7 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
@@ -5561,7 +5561,7 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
@@ -5796,7 +5796,7 @@
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
@@ -6301,7 +6301,7 @@
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
@@ -6348,7 +6348,7 @@
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H113" s="2" t="inlineStr">
@@ -6395,7 +6395,7 @@
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H114" s="2" t="inlineStr">
@@ -6489,7 +6489,7 @@
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr">
@@ -6583,7 +6583,7 @@
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr">
@@ -6630,7 +6630,7 @@
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr">
@@ -6724,7 +6724,7 @@
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H121" s="2" t="inlineStr">
@@ -6771,7 +6771,7 @@
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H122" s="2" t="inlineStr">
@@ -7006,7 +7006,7 @@
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H127" s="2" t="inlineStr">
@@ -7507,7 +7507,7 @@
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H138" s="2" t="inlineStr">
@@ -7554,7 +7554,7 @@
       </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H139" s="2" t="inlineStr">
@@ -7601,7 +7601,7 @@
       </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H140" s="2" t="inlineStr">
@@ -7695,7 +7695,7 @@
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H142" s="2" t="inlineStr">
@@ -7789,7 +7789,7 @@
       </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H144" s="2" t="inlineStr">
@@ -7836,7 +7836,7 @@
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H145" s="2" t="inlineStr">
@@ -7930,7 +7930,7 @@
       </c>
       <c r="G147" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H147" s="2" t="inlineStr">
@@ -7977,7 +7977,7 @@
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H148" s="2" t="inlineStr">
@@ -8212,7 +8212,7 @@
       </c>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H153" s="2" t="inlineStr">
@@ -8717,7 +8717,7 @@
       </c>
       <c r="G164" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H164" s="2" t="inlineStr">
@@ -8858,7 +8858,7 @@
       </c>
       <c r="G167" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H167" s="2" t="inlineStr">
@@ -8999,7 +8999,7 @@
       </c>
       <c r="G170" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H170" s="2" t="inlineStr">
@@ -9187,7 +9187,7 @@
       </c>
       <c r="G174" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H174" s="2" t="inlineStr">
@@ -9970,7 +9970,7 @@
       </c>
       <c r="G191" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H191" s="2" t="inlineStr">
@@ -10111,7 +10111,7 @@
       </c>
       <c r="G194" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H194" s="2" t="inlineStr">
@@ -10252,7 +10252,7 @@
       </c>
       <c r="G197" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H197" s="2" t="inlineStr">
@@ -10440,7 +10440,7 @@
       </c>
       <c r="G201" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H201" s="2" t="inlineStr">
@@ -11223,7 +11223,7 @@
       </c>
       <c r="G218" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H218" s="2" t="inlineStr">
@@ -11364,7 +11364,7 @@
       </c>
       <c r="G221" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H221" s="2" t="inlineStr">
@@ -11505,7 +11505,7 @@
       </c>
       <c r="G224" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H224" s="2" t="inlineStr">
@@ -11693,7 +11693,7 @@
       </c>
       <c r="G228" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H228" s="2" t="inlineStr">
@@ -12472,7 +12472,7 @@
       </c>
       <c r="G245" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H245" s="2" t="inlineStr">
@@ -12613,7 +12613,7 @@
       </c>
       <c r="G248" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H248" s="2" t="inlineStr">
@@ -12754,7 +12754,7 @@
       </c>
       <c r="G251" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H251" s="2" t="inlineStr">
@@ -12942,7 +12942,7 @@
       </c>
       <c r="G255" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H255" s="2" t="inlineStr">
@@ -13725,7 +13725,7 @@
       </c>
       <c r="G272" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H272" s="2" t="inlineStr">
@@ -13866,7 +13866,7 @@
       </c>
       <c r="G275" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H275" s="2" t="inlineStr">
@@ -14007,7 +14007,7 @@
       </c>
       <c r="G278" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H278" s="2" t="inlineStr">
@@ -14195,7 +14195,7 @@
       </c>
       <c r="G282" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H282" s="2" t="inlineStr">
@@ -14978,7 +14978,7 @@
       </c>
       <c r="G299" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H299" s="2" t="inlineStr">
@@ -15119,7 +15119,7 @@
       </c>
       <c r="G302" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H302" s="2" t="inlineStr">
@@ -15260,7 +15260,7 @@
       </c>
       <c r="G305" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H305" s="2" t="inlineStr">
@@ -15448,7 +15448,7 @@
       </c>
       <c r="G309" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H309" s="2" t="inlineStr">

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B1_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B1_session_analysis.xlsx
@@ -1551,7 +1551,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1961,7 +1961,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -3141,7 +3141,7 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -4351,7 +4351,7 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -4586,7 +4586,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -5561,7 +5561,7 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
@@ -5796,7 +5796,7 @@
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
@@ -6771,7 +6771,7 @@
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H122" s="2" t="inlineStr">
@@ -7006,7 +7006,7 @@
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H127" s="2" t="inlineStr">
@@ -7977,7 +7977,7 @@
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H148" s="2" t="inlineStr">
@@ -8212,7 +8212,7 @@
       </c>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H153" s="2" t="inlineStr">
@@ -8717,7 +8717,7 @@
       </c>
       <c r="G164" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H164" s="2" t="inlineStr">
@@ -8858,7 +8858,7 @@
       </c>
       <c r="G167" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H167" s="2" t="inlineStr">
@@ -8999,7 +8999,7 @@
       </c>
       <c r="G170" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H170" s="2" t="inlineStr">
@@ -9187,7 +9187,7 @@
       </c>
       <c r="G174" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H174" s="2" t="inlineStr">
@@ -9970,7 +9970,7 @@
       </c>
       <c r="G191" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H191" s="2" t="inlineStr">
@@ -10111,7 +10111,7 @@
       </c>
       <c r="G194" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H194" s="2" t="inlineStr">
@@ -10252,7 +10252,7 @@
       </c>
       <c r="G197" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H197" s="2" t="inlineStr">
@@ -10440,7 +10440,7 @@
       </c>
       <c r="G201" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H201" s="2" t="inlineStr">
@@ -11223,7 +11223,7 @@
       </c>
       <c r="G218" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H218" s="2" t="inlineStr">
@@ -11364,7 +11364,7 @@
       </c>
       <c r="G221" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H221" s="2" t="inlineStr">
@@ -11505,7 +11505,7 @@
       </c>
       <c r="G224" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H224" s="2" t="inlineStr">
@@ -11693,7 +11693,7 @@
       </c>
       <c r="G228" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H228" s="2" t="inlineStr">
@@ -12472,7 +12472,7 @@
       </c>
       <c r="G245" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H245" s="2" t="inlineStr">
@@ -12613,7 +12613,7 @@
       </c>
       <c r="G248" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H248" s="2" t="inlineStr">
@@ -12754,7 +12754,7 @@
       </c>
       <c r="G251" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H251" s="2" t="inlineStr">
@@ -12942,7 +12942,7 @@
       </c>
       <c r="G255" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H255" s="2" t="inlineStr">
@@ -13725,7 +13725,7 @@
       </c>
       <c r="G272" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H272" s="2" t="inlineStr">
@@ -13866,7 +13866,7 @@
       </c>
       <c r="G275" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H275" s="2" t="inlineStr">
@@ -14007,7 +14007,7 @@
       </c>
       <c r="G278" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H278" s="2" t="inlineStr">
@@ -14195,7 +14195,7 @@
       </c>
       <c r="G282" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H282" s="2" t="inlineStr">
@@ -14978,7 +14978,7 @@
       </c>
       <c r="G299" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H299" s="2" t="inlineStr">
@@ -15119,7 +15119,7 @@
       </c>
       <c r="G302" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H302" s="2" t="inlineStr">
@@ -15260,7 +15260,7 @@
       </c>
       <c r="G305" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H305" s="2" t="inlineStr">
@@ -15448,7 +15448,7 @@
       </c>
       <c r="G309" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H309" s="2" t="inlineStr">

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B1_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B1_session_analysis.xlsx
@@ -1551,7 +1551,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1961,7 +1961,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -3141,7 +3141,7 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -4351,7 +4351,7 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -4586,7 +4586,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -5561,7 +5561,7 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
@@ -5796,7 +5796,7 @@
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
@@ -6771,7 +6771,7 @@
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H122" s="2" t="inlineStr">
@@ -7006,7 +7006,7 @@
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H127" s="2" t="inlineStr">
@@ -7977,7 +7977,7 @@
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H148" s="2" t="inlineStr">
@@ -8212,7 +8212,7 @@
       </c>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H153" s="2" t="inlineStr">
@@ -8717,7 +8717,7 @@
       </c>
       <c r="G164" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H164" s="2" t="inlineStr">
@@ -8858,7 +8858,7 @@
       </c>
       <c r="G167" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H167" s="2" t="inlineStr">
@@ -8999,7 +8999,7 @@
       </c>
       <c r="G170" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H170" s="2" t="inlineStr">
@@ -9187,7 +9187,7 @@
       </c>
       <c r="G174" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H174" s="2" t="inlineStr">
@@ -9970,7 +9970,7 @@
       </c>
       <c r="G191" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H191" s="2" t="inlineStr">
@@ -10111,7 +10111,7 @@
       </c>
       <c r="G194" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H194" s="2" t="inlineStr">
@@ -10252,7 +10252,7 @@
       </c>
       <c r="G197" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H197" s="2" t="inlineStr">
@@ -10440,7 +10440,7 @@
       </c>
       <c r="G201" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H201" s="2" t="inlineStr">
@@ -11223,7 +11223,7 @@
       </c>
       <c r="G218" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H218" s="2" t="inlineStr">
@@ -11364,7 +11364,7 @@
       </c>
       <c r="G221" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H221" s="2" t="inlineStr">
@@ -11505,7 +11505,7 @@
       </c>
       <c r="G224" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H224" s="2" t="inlineStr">
@@ -11693,7 +11693,7 @@
       </c>
       <c r="G228" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H228" s="2" t="inlineStr">
@@ -12472,7 +12472,7 @@
       </c>
       <c r="G245" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H245" s="2" t="inlineStr">
@@ -12613,7 +12613,7 @@
       </c>
       <c r="G248" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H248" s="2" t="inlineStr">
@@ -12754,7 +12754,7 @@
       </c>
       <c r="G251" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H251" s="2" t="inlineStr">
@@ -12942,7 +12942,7 @@
       </c>
       <c r="G255" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H255" s="2" t="inlineStr">
@@ -13725,7 +13725,7 @@
       </c>
       <c r="G272" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H272" s="2" t="inlineStr">
@@ -13866,7 +13866,7 @@
       </c>
       <c r="G275" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H275" s="2" t="inlineStr">
@@ -14007,7 +14007,7 @@
       </c>
       <c r="G278" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H278" s="2" t="inlineStr">
@@ -14195,7 +14195,7 @@
       </c>
       <c r="G282" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H282" s="2" t="inlineStr">
@@ -14978,7 +14978,7 @@
       </c>
       <c r="G299" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H299" s="2" t="inlineStr">
@@ -15119,7 +15119,7 @@
       </c>
       <c r="G302" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H302" s="2" t="inlineStr">
@@ -15260,7 +15260,7 @@
       </c>
       <c r="G305" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H305" s="2" t="inlineStr">
@@ -15448,7 +15448,7 @@
       </c>
       <c r="G309" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H309" s="2" t="inlineStr">

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B1_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B1_session_analysis.xlsx
@@ -898,7 +898,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -953,7 +953,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1010,7 +1010,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1114,7 +1114,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1213,7 +1213,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1305,7 +1305,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -2671,7 +2671,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -2718,7 +2718,7 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -2859,7 +2859,7 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -2953,7 +2953,7 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -3000,7 +3000,7 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -3094,7 +3094,7 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -3928,7 +3928,7 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -3975,7 +3975,7 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -4069,7 +4069,7 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -4163,7 +4163,7 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -4210,7 +4210,7 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -4304,7 +4304,7 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -5091,7 +5091,7 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
@@ -5138,7 +5138,7 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
@@ -5185,7 +5185,7 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
@@ -5279,7 +5279,7 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
@@ -5373,7 +5373,7 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
@@ -5420,7 +5420,7 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
@@ -5514,7 +5514,7 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
@@ -6301,7 +6301,7 @@
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
@@ -6348,7 +6348,7 @@
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H113" s="2" t="inlineStr">
@@ -6395,7 +6395,7 @@
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H114" s="2" t="inlineStr">
@@ -6489,7 +6489,7 @@
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr">
@@ -6583,7 +6583,7 @@
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr">
@@ -6630,7 +6630,7 @@
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr">
@@ -6724,7 +6724,7 @@
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H121" s="2" t="inlineStr">
@@ -7507,7 +7507,7 @@
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H138" s="2" t="inlineStr">
@@ -7554,7 +7554,7 @@
       </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H139" s="2" t="inlineStr">
@@ -7601,7 +7601,7 @@
       </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H140" s="2" t="inlineStr">
@@ -7695,7 +7695,7 @@
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H142" s="2" t="inlineStr">
@@ -7789,7 +7789,7 @@
       </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H144" s="2" t="inlineStr">
@@ -7836,7 +7836,7 @@
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H145" s="2" t="inlineStr">
@@ -7930,7 +7930,7 @@
       </c>
       <c r="G147" s="2" t="inlineStr">
         <is>
-          <t>System, dnasr281@gmail.com</t>
+          <t>dnasr281@gmail.com, System</t>
         </is>
       </c>
       <c r="H147" s="2" t="inlineStr">

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B1_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B1_session_analysis.xlsx
@@ -898,7 +898,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -953,7 +953,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1010,7 +1010,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1114,7 +1114,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1213,7 +1213,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1305,7 +1305,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -2671,7 +2671,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -2718,7 +2718,7 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -2859,7 +2859,7 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -2953,7 +2953,7 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -3000,7 +3000,7 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -3094,7 +3094,7 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -3928,7 +3928,7 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -3975,7 +3975,7 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -4069,7 +4069,7 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -4163,7 +4163,7 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -4210,7 +4210,7 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -4304,7 +4304,7 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -5091,7 +5091,7 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
@@ -5138,7 +5138,7 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
@@ -5185,7 +5185,7 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
@@ -5279,7 +5279,7 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
@@ -5373,7 +5373,7 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
@@ -5420,7 +5420,7 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
@@ -5514,7 +5514,7 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
@@ -6301,7 +6301,7 @@
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
@@ -6348,7 +6348,7 @@
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H113" s="2" t="inlineStr">
@@ -6395,7 +6395,7 @@
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H114" s="2" t="inlineStr">
@@ -6489,7 +6489,7 @@
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr">
@@ -6583,7 +6583,7 @@
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr">
@@ -6630,7 +6630,7 @@
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr">
@@ -6724,7 +6724,7 @@
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H121" s="2" t="inlineStr">
@@ -7507,7 +7507,7 @@
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H138" s="2" t="inlineStr">
@@ -7554,7 +7554,7 @@
       </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H139" s="2" t="inlineStr">
@@ -7601,7 +7601,7 @@
       </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H140" s="2" t="inlineStr">
@@ -7695,7 +7695,7 @@
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H142" s="2" t="inlineStr">
@@ -7789,7 +7789,7 @@
       </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H144" s="2" t="inlineStr">
@@ -7836,7 +7836,7 @@
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H145" s="2" t="inlineStr">
@@ -7930,7 +7930,7 @@
       </c>
       <c r="G147" s="2" t="inlineStr">
         <is>
-          <t>dnasr281@gmail.com, System</t>
+          <t>System, dnasr281@gmail.com</t>
         </is>
       </c>
       <c r="H147" s="2" t="inlineStr">

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B1_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B1_session_analysis.xlsx
@@ -953,7 +953,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1010,7 +1010,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1114,7 +1114,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1213,7 +1213,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1305,7 +1305,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1387,7 +1387,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1551,7 +1551,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1797,7 +1797,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1961,7 +1961,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -2718,7 +2718,7 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -2859,7 +2859,7 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -2953,7 +2953,7 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -3000,7 +3000,7 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -3047,7 +3047,7 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -3094,7 +3094,7 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -3141,7 +3141,7 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -3282,7 +3282,7 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -3928,7 +3928,7 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -3975,7 +3975,7 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -4069,7 +4069,7 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -4163,7 +4163,7 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -4210,7 +4210,7 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -4257,7 +4257,7 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -4304,7 +4304,7 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -4351,7 +4351,7 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -4492,7 +4492,7 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -4586,7 +4586,7 @@
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -5138,7 +5138,7 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
@@ -5185,7 +5185,7 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
@@ -5279,7 +5279,7 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
@@ -5373,7 +5373,7 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
@@ -5420,7 +5420,7 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
@@ -5467,7 +5467,7 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
@@ -5514,7 +5514,7 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
@@ -5561,7 +5561,7 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
@@ -5702,7 +5702,7 @@
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
@@ -5796,7 +5796,7 @@
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
@@ -6348,7 +6348,7 @@
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H113" s="2" t="inlineStr">
@@ -6395,7 +6395,7 @@
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H114" s="2" t="inlineStr">
@@ -6489,7 +6489,7 @@
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr">
@@ -6583,7 +6583,7 @@
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr">
@@ -6630,7 +6630,7 @@
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr">
@@ -6677,7 +6677,7 @@
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr">
@@ -6724,7 +6724,7 @@
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H121" s="2" t="inlineStr">
@@ -6771,7 +6771,7 @@
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H122" s="2" t="inlineStr">
@@ -6912,7 +6912,7 @@
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H125" s="2" t="inlineStr">
@@ -7006,7 +7006,7 @@
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H127" s="2" t="inlineStr">
@@ -7554,7 +7554,7 @@
       </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H139" s="2" t="inlineStr">
@@ -7601,7 +7601,7 @@
       </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H140" s="2" t="inlineStr">
@@ -7695,7 +7695,7 @@
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H142" s="2" t="inlineStr">
@@ -7789,7 +7789,7 @@
       </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H144" s="2" t="inlineStr">
@@ -7836,7 +7836,7 @@
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H145" s="2" t="inlineStr">
@@ -7883,7 +7883,7 @@
       </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H146" s="2" t="inlineStr">
@@ -7930,7 +7930,7 @@
       </c>
       <c r="G147" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H147" s="2" t="inlineStr">
@@ -7977,7 +7977,7 @@
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H148" s="2" t="inlineStr">
@@ -8118,7 +8118,7 @@
       </c>
       <c r="G151" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H151" s="2" t="inlineStr">
@@ -8212,7 +8212,7 @@
       </c>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H153" s="2" t="inlineStr">
@@ -8717,7 +8717,7 @@
       </c>
       <c r="G164" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H164" s="2" t="inlineStr">
@@ -8858,7 +8858,7 @@
       </c>
       <c r="G167" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H167" s="2" t="inlineStr">
@@ -8999,7 +8999,7 @@
       </c>
       <c r="G170" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H170" s="2" t="inlineStr">
@@ -9187,7 +9187,7 @@
       </c>
       <c r="G174" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H174" s="2" t="inlineStr">
@@ -9234,7 +9234,7 @@
       </c>
       <c r="G175" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H175" s="2" t="inlineStr">
@@ -9281,7 +9281,7 @@
       </c>
       <c r="G176" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H176" s="2" t="inlineStr">
@@ -9328,7 +9328,7 @@
       </c>
       <c r="G177" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H177" s="2" t="inlineStr">
@@ -9970,7 +9970,7 @@
       </c>
       <c r="G191" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H191" s="2" t="inlineStr">
@@ -10111,7 +10111,7 @@
       </c>
       <c r="G194" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H194" s="2" t="inlineStr">
@@ -10252,7 +10252,7 @@
       </c>
       <c r="G197" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H197" s="2" t="inlineStr">
@@ -10440,7 +10440,7 @@
       </c>
       <c r="G201" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H201" s="2" t="inlineStr">
@@ -10487,7 +10487,7 @@
       </c>
       <c r="G202" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H202" s="2" t="inlineStr">
@@ -10534,7 +10534,7 @@
       </c>
       <c r="G203" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H203" s="2" t="inlineStr">
@@ -10581,7 +10581,7 @@
       </c>
       <c r="G204" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H204" s="2" t="inlineStr">
@@ -11223,7 +11223,7 @@
       </c>
       <c r="G218" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H218" s="2" t="inlineStr">
@@ -11364,7 +11364,7 @@
       </c>
       <c r="G221" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H221" s="2" t="inlineStr">
@@ -11505,7 +11505,7 @@
       </c>
       <c r="G224" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H224" s="2" t="inlineStr">
@@ -11693,7 +11693,7 @@
       </c>
       <c r="G228" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H228" s="2" t="inlineStr">
@@ -11740,7 +11740,7 @@
       </c>
       <c r="G229" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H229" s="2" t="inlineStr">
@@ -11787,7 +11787,7 @@
       </c>
       <c r="G230" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H230" s="2" t="inlineStr">
@@ -11834,7 +11834,7 @@
       </c>
       <c r="G231" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H231" s="2" t="inlineStr">
@@ -12472,7 +12472,7 @@
       </c>
       <c r="G245" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H245" s="2" t="inlineStr">
@@ -12613,7 +12613,7 @@
       </c>
       <c r="G248" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H248" s="2" t="inlineStr">
@@ -12754,7 +12754,7 @@
       </c>
       <c r="G251" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H251" s="2" t="inlineStr">
@@ -12942,7 +12942,7 @@
       </c>
       <c r="G255" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H255" s="2" t="inlineStr">
@@ -12989,7 +12989,7 @@
       </c>
       <c r="G256" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H256" s="2" t="inlineStr">
@@ -13036,7 +13036,7 @@
       </c>
       <c r="G257" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H257" s="2" t="inlineStr">
@@ -13083,7 +13083,7 @@
       </c>
       <c r="G258" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H258" s="2" t="inlineStr">
@@ -13725,7 +13725,7 @@
       </c>
       <c r="G272" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H272" s="2" t="inlineStr">
@@ -13866,7 +13866,7 @@
       </c>
       <c r="G275" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H275" s="2" t="inlineStr">
@@ -14007,7 +14007,7 @@
       </c>
       <c r="G278" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H278" s="2" t="inlineStr">
@@ -14195,7 +14195,7 @@
       </c>
       <c r="G282" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H282" s="2" t="inlineStr">
@@ -14242,7 +14242,7 @@
       </c>
       <c r="G283" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H283" s="2" t="inlineStr">
@@ -14289,7 +14289,7 @@
       </c>
       <c r="G284" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H284" s="2" t="inlineStr">
@@ -14336,7 +14336,7 @@
       </c>
       <c r="G285" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H285" s="2" t="inlineStr">
@@ -14978,7 +14978,7 @@
       </c>
       <c r="G299" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H299" s="2" t="inlineStr">
@@ -15119,7 +15119,7 @@
       </c>
       <c r="G302" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H302" s="2" t="inlineStr">
@@ -15260,7 +15260,7 @@
       </c>
       <c r="G305" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H305" s="2" t="inlineStr">
@@ -15448,7 +15448,7 @@
       </c>
       <c r="G309" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H309" s="2" t="inlineStr">
@@ -15495,7 +15495,7 @@
       </c>
       <c r="G310" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H310" s="2" t="inlineStr">
@@ -15542,7 +15542,7 @@
       </c>
       <c r="G311" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H311" s="2" t="inlineStr">
@@ -15589,7 +15589,7 @@
       </c>
       <c r="G312" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H312" s="2" t="inlineStr">

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B1_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B1_session_analysis.xlsx
@@ -898,7 +898,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1067,7 +1067,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -2671,7 +2671,7 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -2812,7 +2812,7 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -4022,7 +4022,7 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -5091,7 +5091,7 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
@@ -5232,7 +5232,7 @@
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
@@ -6301,7 +6301,7 @@
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
@@ -6442,7 +6442,7 @@
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H115" s="2" t="inlineStr">
@@ -7507,7 +7507,7 @@
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H138" s="2" t="inlineStr">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="G141" s="2" t="inlineStr">
         <is>
-          <t>Administrator, Miss Dina Nasr</t>
+          <t>Miss Dina Nasr, Administrator</t>
         </is>
       </c>
       <c r="H141" s="2" t="inlineStr">

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B1_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B1_session_analysis.xlsx
@@ -479,7 +479,7 @@
     <col width="9" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="31" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="22" customWidth="1" min="11" max="11"/>
@@ -571,11 +571,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
         <is>
           <t>10/26</t>
@@ -676,11 +672,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G4" s="2" t="inlineStr"/>
       <c r="H4" s="2" t="inlineStr">
         <is>
           <t>22/26</t>
@@ -731,11 +723,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G5" s="2" t="inlineStr"/>
       <c r="H5" s="2" t="inlineStr">
         <is>
           <t>26/26</t>
@@ -786,11 +774,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G6" s="2" t="inlineStr"/>
       <c r="H6" s="2" t="inlineStr">
         <is>
           <t>22/26</t>
@@ -841,11 +825,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G7" s="2" t="inlineStr"/>
       <c r="H7" s="2" t="inlineStr">
         <is>
           <t>20/26</t>
@@ -896,11 +876,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G8" s="2" t="inlineStr"/>
       <c r="H8" s="2" t="inlineStr">
         <is>
           <t>26/26</t>
@@ -951,11 +927,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G9" s="2" t="inlineStr"/>
       <c r="H9" s="2" t="inlineStr">
         <is>
           <t>21/26</t>
@@ -1008,11 +980,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G10" s="2" t="inlineStr"/>
       <c r="H10" s="2" t="inlineStr">
         <is>
           <t>20/26</t>
@@ -1065,11 +1033,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G11" s="2" t="inlineStr"/>
       <c r="H11" s="2" t="inlineStr">
         <is>
           <t>24/26</t>
@@ -1112,11 +1076,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G12" s="2" t="inlineStr"/>
       <c r="H12" s="2" t="inlineStr">
         <is>
           <t>19/26</t>
@@ -1159,11 +1119,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G13" s="2" t="inlineStr"/>
       <c r="H13" s="2" t="inlineStr">
         <is>
           <t>24/26</t>
@@ -1211,11 +1167,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G14" s="2" t="inlineStr"/>
       <c r="H14" s="2" t="inlineStr">
         <is>
           <t>25/26</t>
@@ -1303,11 +1255,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G15" s="2" t="inlineStr"/>
       <c r="H15" s="2" t="inlineStr">
         <is>
           <t>22/26</t>
@@ -1385,11 +1333,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G16" s="2" t="inlineStr"/>
       <c r="H16" s="2" t="inlineStr">
         <is>
           <t>22/26</t>
@@ -1467,11 +1411,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G17" s="2" t="inlineStr"/>
       <c r="H17" s="2" t="inlineStr">
         <is>
           <t>18/26</t>
@@ -1549,11 +1489,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G18" s="2" t="inlineStr"/>
       <c r="H18" s="2" t="inlineStr">
         <is>
           <t>22/26</t>
@@ -1631,11 +1567,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G19" s="2" t="inlineStr"/>
       <c r="H19" s="2" t="inlineStr">
         <is>
           <t>19/26</t>
@@ -1713,11 +1645,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G20" s="2" t="inlineStr"/>
       <c r="H20" s="2" t="inlineStr">
         <is>
           <t>20/26</t>
@@ -1795,11 +1723,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G21" s="2" t="inlineStr"/>
       <c r="H21" s="2" t="inlineStr">
         <is>
           <t>26/26</t>
@@ -1877,11 +1801,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G22" s="2" t="inlineStr"/>
       <c r="H22" s="2" t="inlineStr">
         <is>
           <t>18/26</t>
@@ -1959,11 +1879,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G23" s="2" t="inlineStr"/>
       <c r="H23" s="2" t="inlineStr">
         <is>
           <t>20/26</t>
@@ -2041,11 +1957,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G24" s="2" t="inlineStr"/>
       <c r="H24" s="2" t="inlineStr">
         <is>
           <t>16/26</t>
@@ -2322,11 +2234,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G28" s="2" t="inlineStr"/>
       <c r="H28" s="2" t="inlineStr">
         <is>
           <t>17/27</t>
@@ -2369,11 +2277,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G29" s="2" t="inlineStr"/>
       <c r="H29" s="2" t="inlineStr">
         <is>
           <t>1/27</t>
@@ -2421,11 +2325,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G30" s="2" t="inlineStr"/>
       <c r="H30" s="2" t="inlineStr">
         <is>
           <t>20/27</t>
@@ -2483,11 +2383,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G31" s="2" t="inlineStr"/>
       <c r="H31" s="2" t="inlineStr">
         <is>
           <t>27/27</t>
@@ -2545,11 +2441,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G32" s="2" t="inlineStr"/>
       <c r="H32" s="2" t="inlineStr">
         <is>
           <t>24/27</t>
@@ -2607,11 +2499,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G33" s="2" t="inlineStr"/>
       <c r="H33" s="2" t="inlineStr">
         <is>
           <t>21/27</t>
@@ -2669,11 +2557,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G34" s="2" t="inlineStr"/>
       <c r="H34" s="2" t="inlineStr">
         <is>
           <t>25/27</t>
@@ -2716,11 +2600,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G35" s="2" t="inlineStr"/>
       <c r="H35" s="2" t="inlineStr">
         <is>
           <t>24/27</t>
@@ -2763,11 +2643,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G36" s="2" t="inlineStr"/>
       <c r="H36" s="2" t="inlineStr">
         <is>
           <t>23/27</t>
@@ -2810,11 +2686,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G37" s="2" t="inlineStr"/>
       <c r="H37" s="2" t="inlineStr">
         <is>
           <t>22/27</t>
@@ -2857,11 +2729,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G38" s="2" t="inlineStr"/>
       <c r="H38" s="2" t="inlineStr">
         <is>
           <t>26/27</t>
@@ -2904,11 +2772,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G39" s="2" t="inlineStr"/>
       <c r="H39" s="2" t="inlineStr">
         <is>
           <t>24/27</t>
@@ -2951,11 +2815,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G40" s="2" t="inlineStr"/>
       <c r="H40" s="2" t="inlineStr">
         <is>
           <t>26/27</t>
@@ -2998,11 +2858,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G41" s="2" t="inlineStr"/>
       <c r="H41" s="2" t="inlineStr">
         <is>
           <t>24/27</t>
@@ -3045,11 +2901,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G42" s="2" t="inlineStr"/>
       <c r="H42" s="2" t="inlineStr">
         <is>
           <t>24/27</t>
@@ -3092,11 +2944,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G43" s="2" t="inlineStr"/>
       <c r="H43" s="2" t="inlineStr">
         <is>
           <t>22/27</t>
@@ -3139,11 +2987,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G44" s="2" t="inlineStr"/>
       <c r="H44" s="2" t="inlineStr">
         <is>
           <t>24/27</t>
@@ -3186,11 +3030,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G45" s="2" t="inlineStr"/>
       <c r="H45" s="2" t="inlineStr">
         <is>
           <t>20/27</t>
@@ -3233,11 +3073,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G46" s="2" t="inlineStr"/>
       <c r="H46" s="2" t="inlineStr">
         <is>
           <t>20/27</t>
@@ -3280,11 +3116,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G47" s="2" t="inlineStr"/>
       <c r="H47" s="2" t="inlineStr">
         <is>
           <t>27/27</t>
@@ -3327,11 +3159,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G48" s="2" t="inlineStr"/>
       <c r="H48" s="2" t="inlineStr">
         <is>
           <t>23/27</t>
@@ -3374,11 +3202,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G49" s="2" t="inlineStr"/>
       <c r="H49" s="2" t="inlineStr">
         <is>
           <t>23/27</t>
@@ -3421,11 +3245,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G50" s="2" t="inlineStr"/>
       <c r="H50" s="2" t="inlineStr">
         <is>
           <t>17/27</t>
@@ -3597,11 +3417,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G54" s="2" t="inlineStr"/>
       <c r="H54" s="2" t="inlineStr">
         <is>
           <t>13/26</t>
@@ -3644,11 +3460,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G55" s="2" t="inlineStr"/>
       <c r="H55" s="2" t="inlineStr">
         <is>
           <t>20/26</t>
@@ -3691,11 +3503,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G56" s="2" t="inlineStr"/>
       <c r="H56" s="2" t="inlineStr">
         <is>
           <t>1/26</t>
@@ -3738,11 +3546,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G57" s="2" t="inlineStr"/>
       <c r="H57" s="2" t="inlineStr">
         <is>
           <t>25/26</t>
@@ -3785,11 +3589,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G58" s="2" t="inlineStr"/>
       <c r="H58" s="2" t="inlineStr">
         <is>
           <t>19/26</t>
@@ -3832,11 +3632,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G59" s="2" t="inlineStr"/>
       <c r="H59" s="2" t="inlineStr">
         <is>
           <t>21/26</t>
@@ -3879,11 +3675,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G60" s="2" t="inlineStr"/>
       <c r="H60" s="2" t="inlineStr">
         <is>
           <t>25/26</t>
@@ -3926,11 +3718,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G61" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G61" s="2" t="inlineStr"/>
       <c r="H61" s="2" t="inlineStr">
         <is>
           <t>20/26</t>
@@ -3973,11 +3761,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G62" s="2" t="inlineStr"/>
       <c r="H62" s="2" t="inlineStr">
         <is>
           <t>19/26</t>
@@ -4020,11 +3804,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G63" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G63" s="2" t="inlineStr"/>
       <c r="H63" s="2" t="inlineStr">
         <is>
           <t>16/26</t>
@@ -4067,11 +3847,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G64" s="2" t="inlineStr"/>
       <c r="H64" s="2" t="inlineStr">
         <is>
           <t>17/26</t>
@@ -4114,11 +3890,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G65" s="2" t="inlineStr"/>
       <c r="H65" s="2" t="inlineStr">
         <is>
           <t>20/26</t>
@@ -4161,11 +3933,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G66" s="2" t="inlineStr"/>
       <c r="H66" s="2" t="inlineStr">
         <is>
           <t>22/26</t>
@@ -4208,11 +3976,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G67" s="2" t="inlineStr"/>
       <c r="H67" s="2" t="inlineStr">
         <is>
           <t>19/26</t>
@@ -4255,11 +4019,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G68" s="2" t="inlineStr"/>
       <c r="H68" s="2" t="inlineStr">
         <is>
           <t>21/26</t>
@@ -4302,11 +4062,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G69" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G69" s="2" t="inlineStr"/>
       <c r="H69" s="2" t="inlineStr">
         <is>
           <t>19/26</t>
@@ -4349,11 +4105,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G70" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G70" s="2" t="inlineStr"/>
       <c r="H70" s="2" t="inlineStr">
         <is>
           <t>18/26</t>
@@ -4396,11 +4148,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G71" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G71" s="2" t="inlineStr"/>
       <c r="H71" s="2" t="inlineStr">
         <is>
           <t>17/26</t>
@@ -4443,11 +4191,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G72" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G72" s="2" t="inlineStr"/>
       <c r="H72" s="2" t="inlineStr">
         <is>
           <t>18/26</t>
@@ -4490,11 +4234,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G73" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G73" s="2" t="inlineStr"/>
       <c r="H73" s="2" t="inlineStr">
         <is>
           <t>26/26</t>
@@ -4537,11 +4277,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G74" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G74" s="2" t="inlineStr"/>
       <c r="H74" s="2" t="inlineStr">
         <is>
           <t>23/26</t>
@@ -4584,11 +4320,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G75" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G75" s="2" t="inlineStr"/>
       <c r="H75" s="2" t="inlineStr">
         <is>
           <t>21/26</t>
@@ -4631,11 +4363,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G76" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G76" s="2" t="inlineStr"/>
       <c r="H76" s="2" t="inlineStr">
         <is>
           <t>21/26</t>
@@ -4807,11 +4535,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G80" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G80" s="2" t="inlineStr"/>
       <c r="H80" s="2" t="inlineStr">
         <is>
           <t>10/27</t>
@@ -4854,11 +4578,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G81" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G81" s="2" t="inlineStr"/>
       <c r="H81" s="2" t="inlineStr">
         <is>
           <t>21/27</t>
@@ -4901,11 +4621,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G82" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G82" s="2" t="inlineStr"/>
       <c r="H82" s="2" t="inlineStr">
         <is>
           <t>2/27</t>
@@ -4948,11 +4664,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G83" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G83" s="2" t="inlineStr"/>
       <c r="H83" s="2" t="inlineStr">
         <is>
           <t>25/27</t>
@@ -4995,11 +4707,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G84" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G84" s="2" t="inlineStr"/>
       <c r="H84" s="2" t="inlineStr">
         <is>
           <t>22/27</t>
@@ -5042,11 +4750,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G85" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G85" s="2" t="inlineStr"/>
       <c r="H85" s="2" t="inlineStr">
         <is>
           <t>23/27</t>
@@ -5089,11 +4793,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G86" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G86" s="2" t="inlineStr"/>
       <c r="H86" s="2" t="inlineStr">
         <is>
           <t>24/27</t>
@@ -5136,11 +4836,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G87" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G87" s="2" t="inlineStr"/>
       <c r="H87" s="2" t="inlineStr">
         <is>
           <t>22/27</t>
@@ -5183,11 +4879,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G88" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G88" s="2" t="inlineStr"/>
       <c r="H88" s="2" t="inlineStr">
         <is>
           <t>19/27</t>
@@ -5230,11 +4922,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G89" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G89" s="2" t="inlineStr"/>
       <c r="H89" s="2" t="inlineStr">
         <is>
           <t>24/27</t>
@@ -5277,11 +4965,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G90" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G90" s="2" t="inlineStr"/>
       <c r="H90" s="2" t="inlineStr">
         <is>
           <t>23/27</t>
@@ -5324,11 +5008,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G91" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G91" s="2" t="inlineStr"/>
       <c r="H91" s="2" t="inlineStr">
         <is>
           <t>23/27</t>
@@ -5371,11 +5051,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G92" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G92" s="2" t="inlineStr"/>
       <c r="H92" s="2" t="inlineStr">
         <is>
           <t>26/27</t>
@@ -5418,11 +5094,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G93" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G93" s="2" t="inlineStr"/>
       <c r="H93" s="2" t="inlineStr">
         <is>
           <t>21/27</t>
@@ -5465,11 +5137,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G94" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G94" s="2" t="inlineStr"/>
       <c r="H94" s="2" t="inlineStr">
         <is>
           <t>21/27</t>
@@ -5512,11 +5180,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G95" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G95" s="2" t="inlineStr"/>
       <c r="H95" s="2" t="inlineStr">
         <is>
           <t>24/27</t>
@@ -5559,11 +5223,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G96" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G96" s="2" t="inlineStr"/>
       <c r="H96" s="2" t="inlineStr">
         <is>
           <t>20/27</t>
@@ -5606,11 +5266,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G97" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G97" s="2" t="inlineStr"/>
       <c r="H97" s="2" t="inlineStr">
         <is>
           <t>24/27</t>
@@ -5653,11 +5309,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G98" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G98" s="2" t="inlineStr"/>
       <c r="H98" s="2" t="inlineStr">
         <is>
           <t>27/27</t>
@@ -5700,11 +5352,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G99" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G99" s="2" t="inlineStr"/>
       <c r="H99" s="2" t="inlineStr">
         <is>
           <t>27/27</t>
@@ -5747,11 +5395,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G100" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G100" s="2" t="inlineStr"/>
       <c r="H100" s="2" t="inlineStr">
         <is>
           <t>24/27</t>
@@ -5794,11 +5438,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G101" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G101" s="2" t="inlineStr"/>
       <c r="H101" s="2" t="inlineStr">
         <is>
           <t>18/27</t>
@@ -5841,11 +5481,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G102" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G102" s="2" t="inlineStr"/>
       <c r="H102" s="2" t="inlineStr">
         <is>
           <t>16/27</t>
@@ -6017,11 +5653,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G106" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G106" s="2" t="inlineStr"/>
       <c r="H106" s="2" t="inlineStr">
         <is>
           <t>2/30</t>
@@ -6064,11 +5696,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G107" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G107" s="2" t="inlineStr"/>
       <c r="H107" s="2" t="inlineStr">
         <is>
           <t>14/30</t>
@@ -6111,11 +5739,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G108" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G108" s="2" t="inlineStr"/>
       <c r="H108" s="2" t="inlineStr">
         <is>
           <t>16/30</t>
@@ -6158,11 +5782,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G109" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G109" s="2" t="inlineStr"/>
       <c r="H109" s="2" t="inlineStr">
         <is>
           <t>30/30</t>
@@ -6205,11 +5825,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G110" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G110" s="2" t="inlineStr"/>
       <c r="H110" s="2" t="inlineStr">
         <is>
           <t>23/30</t>
@@ -6252,11 +5868,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G111" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G111" s="2" t="inlineStr"/>
       <c r="H111" s="2" t="inlineStr">
         <is>
           <t>26/30</t>
@@ -6299,11 +5911,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G112" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G112" s="2" t="inlineStr"/>
       <c r="H112" s="2" t="inlineStr">
         <is>
           <t>26/30</t>
@@ -6346,11 +5954,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G113" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G113" s="2" t="inlineStr"/>
       <c r="H113" s="2" t="inlineStr">
         <is>
           <t>27/30</t>
@@ -6393,11 +5997,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G114" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G114" s="2" t="inlineStr"/>
       <c r="H114" s="2" t="inlineStr">
         <is>
           <t>25/30</t>
@@ -6440,11 +6040,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G115" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G115" s="2" t="inlineStr"/>
       <c r="H115" s="2" t="inlineStr">
         <is>
           <t>22/30</t>
@@ -6487,11 +6083,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G116" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G116" s="2" t="inlineStr"/>
       <c r="H116" s="2" t="inlineStr">
         <is>
           <t>24/30</t>
@@ -6534,11 +6126,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G117" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G117" s="2" t="inlineStr"/>
       <c r="H117" s="2" t="inlineStr">
         <is>
           <t>26/30</t>
@@ -6581,11 +6169,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G118" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G118" s="2" t="inlineStr"/>
       <c r="H118" s="2" t="inlineStr">
         <is>
           <t>28/30</t>
@@ -6628,11 +6212,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G119" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G119" s="2" t="inlineStr"/>
       <c r="H119" s="2" t="inlineStr">
         <is>
           <t>29/30</t>
@@ -6675,11 +6255,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G120" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G120" s="2" t="inlineStr"/>
       <c r="H120" s="2" t="inlineStr">
         <is>
           <t>22/30</t>
@@ -6722,11 +6298,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G121" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G121" s="2" t="inlineStr"/>
       <c r="H121" s="2" t="inlineStr">
         <is>
           <t>26/30</t>
@@ -6769,11 +6341,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G122" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G122" s="2" t="inlineStr"/>
       <c r="H122" s="2" t="inlineStr">
         <is>
           <t>22/30</t>
@@ -6816,11 +6384,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G123" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G123" s="2" t="inlineStr"/>
       <c r="H123" s="2" t="inlineStr">
         <is>
           <t>25/30</t>
@@ -6863,11 +6427,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G124" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G124" s="2" t="inlineStr"/>
       <c r="H124" s="2" t="inlineStr">
         <is>
           <t>25/30</t>
@@ -6910,11 +6470,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G125" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G125" s="2" t="inlineStr"/>
       <c r="H125" s="2" t="inlineStr">
         <is>
           <t>30/30</t>
@@ -6957,11 +6513,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G126" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G126" s="2" t="inlineStr"/>
       <c r="H126" s="2" t="inlineStr">
         <is>
           <t>26/30</t>
@@ -7004,11 +6556,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G127" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G127" s="2" t="inlineStr"/>
       <c r="H127" s="2" t="inlineStr">
         <is>
           <t>23/30</t>
@@ -7051,11 +6599,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G128" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G128" s="2" t="inlineStr"/>
       <c r="H128" s="2" t="inlineStr">
         <is>
           <t>21/30</t>
@@ -7270,11 +6814,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G133" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G133" s="2" t="inlineStr"/>
       <c r="H133" s="2" t="inlineStr">
         <is>
           <t>12/23</t>
@@ -7317,11 +6857,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G134" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G134" s="2" t="inlineStr"/>
       <c r="H134" s="2" t="inlineStr">
         <is>
           <t>17/23</t>
@@ -7364,11 +6900,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G135" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G135" s="2" t="inlineStr"/>
       <c r="H135" s="2" t="inlineStr">
         <is>
           <t>23/23</t>
@@ -7411,11 +6943,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G136" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G136" s="2" t="inlineStr"/>
       <c r="H136" s="2" t="inlineStr">
         <is>
           <t>18/23</t>
@@ -7458,11 +6986,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G137" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G137" s="2" t="inlineStr"/>
       <c r="H137" s="2" t="inlineStr">
         <is>
           <t>15/23</t>
@@ -7505,11 +7029,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G138" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G138" s="2" t="inlineStr"/>
       <c r="H138" s="2" t="inlineStr">
         <is>
           <t>21/23</t>
@@ -7552,11 +7072,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G139" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G139" s="2" t="inlineStr"/>
       <c r="H139" s="2" t="inlineStr">
         <is>
           <t>16/23</t>
@@ -7599,11 +7115,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G140" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G140" s="2" t="inlineStr"/>
       <c r="H140" s="2" t="inlineStr">
         <is>
           <t>19/23</t>
@@ -7646,11 +7158,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G141" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G141" s="2" t="inlineStr"/>
       <c r="H141" s="2" t="inlineStr">
         <is>
           <t>20/23</t>
@@ -7693,11 +7201,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G142" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G142" s="2" t="inlineStr"/>
       <c r="H142" s="2" t="inlineStr">
         <is>
           <t>17/23</t>
@@ -7740,11 +7244,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G143" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G143" s="2" t="inlineStr"/>
       <c r="H143" s="2" t="inlineStr">
         <is>
           <t>20/23</t>
@@ -7787,11 +7287,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G144" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G144" s="2" t="inlineStr"/>
       <c r="H144" s="2" t="inlineStr">
         <is>
           <t>23/23</t>
@@ -7834,11 +7330,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G145" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G145" s="2" t="inlineStr"/>
       <c r="H145" s="2" t="inlineStr">
         <is>
           <t>18/23</t>
@@ -7881,11 +7373,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G146" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G146" s="2" t="inlineStr"/>
       <c r="H146" s="2" t="inlineStr">
         <is>
           <t>18/23</t>
@@ -7928,11 +7416,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G147" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G147" s="2" t="inlineStr"/>
       <c r="H147" s="2" t="inlineStr">
         <is>
           <t>21/23</t>
@@ -7975,11 +7459,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G148" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G148" s="2" t="inlineStr"/>
       <c r="H148" s="2" t="inlineStr">
         <is>
           <t>18/23</t>
@@ -8022,11 +7502,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G149" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G149" s="2" t="inlineStr"/>
       <c r="H149" s="2" t="inlineStr">
         <is>
           <t>17/23</t>
@@ -8069,11 +7545,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G150" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G150" s="2" t="inlineStr"/>
       <c r="H150" s="2" t="inlineStr">
         <is>
           <t>18/23</t>
@@ -8116,11 +7588,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G151" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G151" s="2" t="inlineStr"/>
       <c r="H151" s="2" t="inlineStr">
         <is>
           <t>23/23</t>
@@ -8163,11 +7631,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G152" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G152" s="2" t="inlineStr"/>
       <c r="H152" s="2" t="inlineStr">
         <is>
           <t>18/23</t>
@@ -8210,11 +7674,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G153" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G153" s="2" t="inlineStr"/>
       <c r="H153" s="2" t="inlineStr">
         <is>
           <t>16/23</t>
@@ -8257,11 +7717,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G154" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G154" s="2" t="inlineStr"/>
       <c r="H154" s="2" t="inlineStr">
         <is>
           <t>17/23</t>
@@ -8433,11 +7889,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G158" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G158" s="2" t="inlineStr"/>
       <c r="H158" s="2" t="inlineStr">
         <is>
           <t>18/23</t>
@@ -8480,11 +7932,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G159" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G159" s="2" t="inlineStr"/>
       <c r="H159" s="2" t="inlineStr">
         <is>
           <t>1/23</t>
@@ -8527,11 +7975,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G160" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G160" s="2" t="inlineStr"/>
       <c r="H160" s="2" t="inlineStr">
         <is>
           <t>18/23</t>
@@ -8574,11 +8018,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G161" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G161" s="2" t="inlineStr"/>
       <c r="H161" s="2" t="inlineStr">
         <is>
           <t>21/23</t>
@@ -8621,11 +8061,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G162" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G162" s="2" t="inlineStr"/>
       <c r="H162" s="2" t="inlineStr">
         <is>
           <t>18/23</t>
@@ -8668,11 +8104,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G163" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G163" s="2" t="inlineStr"/>
       <c r="H163" s="2" t="inlineStr">
         <is>
           <t>22/23</t>
@@ -8715,11 +8147,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G164" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G164" s="2" t="inlineStr"/>
       <c r="H164" s="2" t="inlineStr">
         <is>
           <t>22/23</t>
@@ -8762,11 +8190,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G165" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G165" s="2" t="inlineStr"/>
       <c r="H165" s="2" t="inlineStr">
         <is>
           <t>14/23</t>
@@ -8809,11 +8233,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G166" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G166" s="2" t="inlineStr"/>
       <c r="H166" s="2" t="inlineStr">
         <is>
           <t>20/23</t>
@@ -8856,11 +8276,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G167" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G167" s="2" t="inlineStr"/>
       <c r="H167" s="2" t="inlineStr">
         <is>
           <t>22/23</t>
@@ -8903,11 +8319,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G168" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G168" s="2" t="inlineStr"/>
       <c r="H168" s="2" t="inlineStr">
         <is>
           <t>19/23</t>
@@ -8950,11 +8362,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G169" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G169" s="2" t="inlineStr"/>
       <c r="H169" s="2" t="inlineStr">
         <is>
           <t>19/23</t>
@@ -8997,11 +8405,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G170" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G170" s="2" t="inlineStr"/>
       <c r="H170" s="2" t="inlineStr">
         <is>
           <t>16/23</t>
@@ -9044,11 +8448,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G171" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G171" s="2" t="inlineStr"/>
       <c r="H171" s="2" t="inlineStr">
         <is>
           <t>20/23</t>
@@ -9091,11 +8491,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G172" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G172" s="2" t="inlineStr"/>
       <c r="H172" s="2" t="inlineStr">
         <is>
           <t>19/23</t>
@@ -9138,11 +8534,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G173" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G173" s="2" t="inlineStr"/>
       <c r="H173" s="2" t="inlineStr">
         <is>
           <t>18/23</t>
@@ -9185,11 +8577,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G174" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G174" s="2" t="inlineStr"/>
       <c r="H174" s="2" t="inlineStr">
         <is>
           <t>19/23</t>
@@ -9232,11 +8620,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G175" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G175" s="2" t="inlineStr"/>
       <c r="H175" s="2" t="inlineStr">
         <is>
           <t>22/23</t>
@@ -9279,11 +8663,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G176" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G176" s="2" t="inlineStr"/>
       <c r="H176" s="2" t="inlineStr">
         <is>
           <t>23/23</t>
@@ -9326,11 +8706,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G177" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G177" s="2" t="inlineStr"/>
       <c r="H177" s="2" t="inlineStr">
         <is>
           <t>23/23</t>
@@ -9373,11 +8749,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G178" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G178" s="2" t="inlineStr"/>
       <c r="H178" s="2" t="inlineStr">
         <is>
           <t>17/23</t>
@@ -9420,11 +8792,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G179" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G179" s="2" t="inlineStr"/>
       <c r="H179" s="2" t="inlineStr">
         <is>
           <t>20/23</t>
@@ -9467,11 +8835,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G180" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G180" s="2" t="inlineStr"/>
       <c r="H180" s="2" t="inlineStr">
         <is>
           <t>19/23</t>
@@ -9686,11 +9050,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G185" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G185" s="2" t="inlineStr"/>
       <c r="H185" s="2" t="inlineStr">
         <is>
           <t>23/30</t>
@@ -9733,11 +9093,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G186" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G186" s="2" t="inlineStr"/>
       <c r="H186" s="2" t="inlineStr">
         <is>
           <t>2/30</t>
@@ -9780,11 +9136,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G187" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G187" s="2" t="inlineStr"/>
       <c r="H187" s="2" t="inlineStr">
         <is>
           <t>23/30</t>
@@ -9827,11 +9179,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G188" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G188" s="2" t="inlineStr"/>
       <c r="H188" s="2" t="inlineStr">
         <is>
           <t>23/30</t>
@@ -9874,11 +9222,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G189" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G189" s="2" t="inlineStr"/>
       <c r="H189" s="2" t="inlineStr">
         <is>
           <t>27/30</t>
@@ -9921,11 +9265,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G190" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G190" s="2" t="inlineStr"/>
       <c r="H190" s="2" t="inlineStr">
         <is>
           <t>26/30</t>
@@ -9968,11 +9308,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G191" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G191" s="2" t="inlineStr"/>
       <c r="H191" s="2" t="inlineStr">
         <is>
           <t>23/30</t>
@@ -10015,11 +9351,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G192" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G192" s="2" t="inlineStr"/>
       <c r="H192" s="2" t="inlineStr">
         <is>
           <t>24/30</t>
@@ -10062,11 +9394,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G193" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G193" s="2" t="inlineStr"/>
       <c r="H193" s="2" t="inlineStr">
         <is>
           <t>24/30</t>
@@ -10109,11 +9437,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G194" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G194" s="2" t="inlineStr"/>
       <c r="H194" s="2" t="inlineStr">
         <is>
           <t>26/30</t>
@@ -10156,11 +9480,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G195" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G195" s="2" t="inlineStr"/>
       <c r="H195" s="2" t="inlineStr">
         <is>
           <t>24/30</t>
@@ -10203,11 +9523,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G196" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G196" s="2" t="inlineStr"/>
       <c r="H196" s="2" t="inlineStr">
         <is>
           <t>27/30</t>
@@ -10250,11 +9566,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G197" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G197" s="2" t="inlineStr"/>
       <c r="H197" s="2" t="inlineStr">
         <is>
           <t>25/30</t>
@@ -10297,11 +9609,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G198" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G198" s="2" t="inlineStr"/>
       <c r="H198" s="2" t="inlineStr">
         <is>
           <t>22/30</t>
@@ -10344,11 +9652,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G199" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G199" s="2" t="inlineStr"/>
       <c r="H199" s="2" t="inlineStr">
         <is>
           <t>26/30</t>
@@ -10391,11 +9695,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G200" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G200" s="2" t="inlineStr"/>
       <c r="H200" s="2" t="inlineStr">
         <is>
           <t>27/30</t>
@@ -10438,11 +9738,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G201" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G201" s="2" t="inlineStr"/>
       <c r="H201" s="2" t="inlineStr">
         <is>
           <t>21/30</t>
@@ -10485,11 +9781,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G202" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G202" s="2" t="inlineStr"/>
       <c r="H202" s="2" t="inlineStr">
         <is>
           <t>27/30</t>
@@ -10532,11 +9824,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G203" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G203" s="2" t="inlineStr"/>
       <c r="H203" s="2" t="inlineStr">
         <is>
           <t>30/30</t>
@@ -10579,11 +9867,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G204" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G204" s="2" t="inlineStr"/>
       <c r="H204" s="2" t="inlineStr">
         <is>
           <t>30/30</t>
@@ -10626,11 +9910,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G205" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G205" s="2" t="inlineStr"/>
       <c r="H205" s="2" t="inlineStr">
         <is>
           <t>26/30</t>
@@ -10673,11 +9953,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G206" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G206" s="2" t="inlineStr"/>
       <c r="H206" s="2" t="inlineStr">
         <is>
           <t>23/30</t>
@@ -10720,11 +9996,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G207" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G207" s="2" t="inlineStr"/>
       <c r="H207" s="2" t="inlineStr">
         <is>
           <t>22/30</t>
@@ -10939,11 +10211,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G212" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G212" s="2" t="inlineStr"/>
       <c r="H212" s="2" t="inlineStr">
         <is>
           <t>20/26</t>
@@ -10986,11 +10254,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G213" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G213" s="2" t="inlineStr"/>
       <c r="H213" s="2" t="inlineStr">
         <is>
           <t>19/26</t>
@@ -11033,11 +10297,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G214" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G214" s="2" t="inlineStr"/>
       <c r="H214" s="2" t="inlineStr">
         <is>
           <t>3/26</t>
@@ -11080,11 +10340,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G215" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G215" s="2" t="inlineStr"/>
       <c r="H215" s="2" t="inlineStr">
         <is>
           <t>24/26</t>
@@ -11127,11 +10383,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G216" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G216" s="2" t="inlineStr"/>
       <c r="H216" s="2" t="inlineStr">
         <is>
           <t>20/26</t>
@@ -11174,11 +10426,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G217" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G217" s="2" t="inlineStr"/>
       <c r="H217" s="2" t="inlineStr">
         <is>
           <t>24/26</t>
@@ -11221,11 +10469,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G218" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G218" s="2" t="inlineStr"/>
       <c r="H218" s="2" t="inlineStr">
         <is>
           <t>26/26</t>
@@ -11268,11 +10512,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G219" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G219" s="2" t="inlineStr"/>
       <c r="H219" s="2" t="inlineStr">
         <is>
           <t>24/26</t>
@@ -11315,11 +10555,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G220" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G220" s="2" t="inlineStr"/>
       <c r="H220" s="2" t="inlineStr">
         <is>
           <t>25/26</t>
@@ -11362,11 +10598,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G221" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G221" s="2" t="inlineStr"/>
       <c r="H221" s="2" t="inlineStr">
         <is>
           <t>25/26</t>
@@ -11409,11 +10641,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G222" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G222" s="2" t="inlineStr"/>
       <c r="H222" s="2" t="inlineStr">
         <is>
           <t>21/26</t>
@@ -11456,11 +10684,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G223" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G223" s="2" t="inlineStr"/>
       <c r="H223" s="2" t="inlineStr">
         <is>
           <t>22/26</t>
@@ -11503,11 +10727,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G224" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G224" s="2" t="inlineStr"/>
       <c r="H224" s="2" t="inlineStr">
         <is>
           <t>22/26</t>
@@ -11550,11 +10770,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G225" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G225" s="2" t="inlineStr"/>
       <c r="H225" s="2" t="inlineStr">
         <is>
           <t>20/26</t>
@@ -11597,11 +10813,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G226" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G226" s="2" t="inlineStr"/>
       <c r="H226" s="2" t="inlineStr">
         <is>
           <t>18/26</t>
@@ -11644,11 +10856,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G227" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G227" s="2" t="inlineStr"/>
       <c r="H227" s="2" t="inlineStr">
         <is>
           <t>21/26</t>
@@ -11691,11 +10899,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G228" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G228" s="2" t="inlineStr"/>
       <c r="H228" s="2" t="inlineStr">
         <is>
           <t>19/26</t>
@@ -11738,11 +10942,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G229" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G229" s="2" t="inlineStr"/>
       <c r="H229" s="2" t="inlineStr">
         <is>
           <t>22/26</t>
@@ -11785,11 +10985,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G230" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G230" s="2" t="inlineStr"/>
       <c r="H230" s="2" t="inlineStr">
         <is>
           <t>26/26</t>
@@ -11832,11 +11028,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G231" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G231" s="2" t="inlineStr"/>
       <c r="H231" s="2" t="inlineStr">
         <is>
           <t>26/26</t>
@@ -11879,11 +11071,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G232" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G232" s="2" t="inlineStr"/>
       <c r="H232" s="2" t="inlineStr">
         <is>
           <t>14/26</t>
@@ -11926,11 +11114,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G233" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G233" s="2" t="inlineStr"/>
       <c r="H233" s="2" t="inlineStr">
         <is>
           <t>21/26</t>
@@ -11973,11 +11157,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G234" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G234" s="2" t="inlineStr"/>
       <c r="H234" s="2" t="inlineStr">
         <is>
           <t>17/26</t>
@@ -12192,11 +11372,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G239" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G239" s="2" t="inlineStr"/>
       <c r="H239" s="2" t="inlineStr">
         <is>
           <t>17/28</t>
@@ -12239,11 +11415,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G240" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G240" s="2" t="inlineStr"/>
       <c r="H240" s="2" t="inlineStr">
         <is>
           <t>17/28</t>
@@ -12329,11 +11501,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G242" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G242" s="2" t="inlineStr"/>
       <c r="H242" s="2" t="inlineStr">
         <is>
           <t>18/28</t>
@@ -12376,11 +11544,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G243" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G243" s="2" t="inlineStr"/>
       <c r="H243" s="2" t="inlineStr">
         <is>
           <t>14/28</t>
@@ -12423,11 +11587,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G244" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G244" s="2" t="inlineStr"/>
       <c r="H244" s="2" t="inlineStr">
         <is>
           <t>21/28</t>
@@ -12470,11 +11630,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G245" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G245" s="2" t="inlineStr"/>
       <c r="H245" s="2" t="inlineStr">
         <is>
           <t>26/28</t>
@@ -12517,11 +11673,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G246" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G246" s="2" t="inlineStr"/>
       <c r="H246" s="2" t="inlineStr">
         <is>
           <t>16/28</t>
@@ -12564,11 +11716,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G247" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G247" s="2" t="inlineStr"/>
       <c r="H247" s="2" t="inlineStr">
         <is>
           <t>19/28</t>
@@ -12611,11 +11759,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G248" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G248" s="2" t="inlineStr"/>
       <c r="H248" s="2" t="inlineStr">
         <is>
           <t>23/28</t>
@@ -12658,11 +11802,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G249" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G249" s="2" t="inlineStr"/>
       <c r="H249" s="2" t="inlineStr">
         <is>
           <t>25/28</t>
@@ -12705,11 +11845,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G250" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G250" s="2" t="inlineStr"/>
       <c r="H250" s="2" t="inlineStr">
         <is>
           <t>21/28</t>
@@ -12752,11 +11888,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G251" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G251" s="2" t="inlineStr"/>
       <c r="H251" s="2" t="inlineStr">
         <is>
           <t>21/28</t>
@@ -12799,11 +11931,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G252" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G252" s="2" t="inlineStr"/>
       <c r="H252" s="2" t="inlineStr">
         <is>
           <t>20/28</t>
@@ -12846,11 +11974,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G253" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G253" s="2" t="inlineStr"/>
       <c r="H253" s="2" t="inlineStr">
         <is>
           <t>21/28</t>
@@ -12893,11 +12017,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G254" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G254" s="2" t="inlineStr"/>
       <c r="H254" s="2" t="inlineStr">
         <is>
           <t>22/28</t>
@@ -12940,11 +12060,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G255" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G255" s="2" t="inlineStr"/>
       <c r="H255" s="2" t="inlineStr">
         <is>
           <t>24/28</t>
@@ -12987,11 +12103,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G256" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G256" s="2" t="inlineStr"/>
       <c r="H256" s="2" t="inlineStr">
         <is>
           <t>25/28</t>
@@ -13034,11 +12146,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G257" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G257" s="2" t="inlineStr"/>
       <c r="H257" s="2" t="inlineStr">
         <is>
           <t>28/28</t>
@@ -13081,11 +12189,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G258" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G258" s="2" t="inlineStr"/>
       <c r="H258" s="2" t="inlineStr">
         <is>
           <t>28/28</t>
@@ -13128,11 +12232,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G259" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G259" s="2" t="inlineStr"/>
       <c r="H259" s="2" t="inlineStr">
         <is>
           <t>21/28</t>
@@ -13175,11 +12275,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G260" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G260" s="2" t="inlineStr"/>
       <c r="H260" s="2" t="inlineStr">
         <is>
           <t>16/28</t>
@@ -13222,11 +12318,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G261" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G261" s="2" t="inlineStr"/>
       <c r="H261" s="2" t="inlineStr">
         <is>
           <t>21/28</t>
@@ -13441,11 +12533,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G266" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G266" s="2" t="inlineStr"/>
       <c r="H266" s="2" t="inlineStr">
         <is>
           <t>2/26</t>
@@ -13488,11 +12576,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G267" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G267" s="2" t="inlineStr"/>
       <c r="H267" s="2" t="inlineStr">
         <is>
           <t>18/26</t>
@@ -13535,11 +12619,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G268" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G268" s="2" t="inlineStr"/>
       <c r="H268" s="2" t="inlineStr">
         <is>
           <t>15/26</t>
@@ -13582,11 +12662,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G269" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G269" s="2" t="inlineStr"/>
       <c r="H269" s="2" t="inlineStr">
         <is>
           <t>21/26</t>
@@ -13629,11 +12705,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G270" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G270" s="2" t="inlineStr"/>
       <c r="H270" s="2" t="inlineStr">
         <is>
           <t>21/26</t>
@@ -13676,11 +12748,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G271" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G271" s="2" t="inlineStr"/>
       <c r="H271" s="2" t="inlineStr">
         <is>
           <t>18/26</t>
@@ -13723,11 +12791,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G272" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G272" s="2" t="inlineStr"/>
       <c r="H272" s="2" t="inlineStr">
         <is>
           <t>21/26</t>
@@ -13770,11 +12834,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G273" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G273" s="2" t="inlineStr"/>
       <c r="H273" s="2" t="inlineStr">
         <is>
           <t>20/26</t>
@@ -13817,11 +12877,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G274" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G274" s="2" t="inlineStr"/>
       <c r="H274" s="2" t="inlineStr">
         <is>
           <t>17/26</t>
@@ -13864,11 +12920,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G275" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G275" s="2" t="inlineStr"/>
       <c r="H275" s="2" t="inlineStr">
         <is>
           <t>20/26</t>
@@ -13911,11 +12963,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G276" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G276" s="2" t="inlineStr"/>
       <c r="H276" s="2" t="inlineStr">
         <is>
           <t>20/26</t>
@@ -13958,11 +13006,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G277" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G277" s="2" t="inlineStr"/>
       <c r="H277" s="2" t="inlineStr">
         <is>
           <t>23/26</t>
@@ -14005,11 +13049,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G278" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G278" s="2" t="inlineStr"/>
       <c r="H278" s="2" t="inlineStr">
         <is>
           <t>21/26</t>
@@ -14052,11 +13092,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G279" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G279" s="2" t="inlineStr"/>
       <c r="H279" s="2" t="inlineStr">
         <is>
           <t>15/26</t>
@@ -14099,11 +13135,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G280" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G280" s="2" t="inlineStr"/>
       <c r="H280" s="2" t="inlineStr">
         <is>
           <t>22/26</t>
@@ -14146,11 +13178,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G281" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G281" s="2" t="inlineStr"/>
       <c r="H281" s="2" t="inlineStr">
         <is>
           <t>19/26</t>
@@ -14193,11 +13221,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G282" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G282" s="2" t="inlineStr"/>
       <c r="H282" s="2" t="inlineStr">
         <is>
           <t>20/26</t>
@@ -14240,11 +13264,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G283" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G283" s="2" t="inlineStr"/>
       <c r="H283" s="2" t="inlineStr">
         <is>
           <t>22/26</t>
@@ -14287,11 +13307,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G284" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G284" s="2" t="inlineStr"/>
       <c r="H284" s="2" t="inlineStr">
         <is>
           <t>26/26</t>
@@ -14334,11 +13350,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G285" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G285" s="2" t="inlineStr"/>
       <c r="H285" s="2" t="inlineStr">
         <is>
           <t>26/26</t>
@@ -14381,11 +13393,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G286" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G286" s="2" t="inlineStr"/>
       <c r="H286" s="2" t="inlineStr">
         <is>
           <t>21/26</t>
@@ -14428,11 +13436,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G287" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G287" s="2" t="inlineStr"/>
       <c r="H287" s="2" t="inlineStr">
         <is>
           <t>18/26</t>
@@ -14475,11 +13479,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G288" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G288" s="2" t="inlineStr"/>
       <c r="H288" s="2" t="inlineStr">
         <is>
           <t>20/26</t>
@@ -14694,11 +13694,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G293" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G293" s="2" t="inlineStr"/>
       <c r="H293" s="2" t="inlineStr">
         <is>
           <t>1/29</t>
@@ -14741,11 +13737,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G294" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G294" s="2" t="inlineStr"/>
       <c r="H294" s="2" t="inlineStr">
         <is>
           <t>20/29</t>
@@ -14788,11 +13780,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G295" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G295" s="2" t="inlineStr"/>
       <c r="H295" s="2" t="inlineStr">
         <is>
           <t>15/29</t>
@@ -14835,11 +13823,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G296" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G296" s="2" t="inlineStr"/>
       <c r="H296" s="2" t="inlineStr">
         <is>
           <t>21/29</t>
@@ -14882,11 +13866,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G297" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G297" s="2" t="inlineStr"/>
       <c r="H297" s="2" t="inlineStr">
         <is>
           <t>21/29</t>
@@ -14929,11 +13909,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G298" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G298" s="2" t="inlineStr"/>
       <c r="H298" s="2" t="inlineStr">
         <is>
           <t>15/29</t>
@@ -14976,11 +13952,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G299" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G299" s="2" t="inlineStr"/>
       <c r="H299" s="2" t="inlineStr">
         <is>
           <t>20/29</t>
@@ -15023,11 +13995,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G300" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G300" s="2" t="inlineStr"/>
       <c r="H300" s="2" t="inlineStr">
         <is>
           <t>22/29</t>
@@ -15070,11 +14038,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G301" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G301" s="2" t="inlineStr"/>
       <c r="H301" s="2" t="inlineStr">
         <is>
           <t>14/29</t>
@@ -15117,11 +14081,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G302" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G302" s="2" t="inlineStr"/>
       <c r="H302" s="2" t="inlineStr">
         <is>
           <t>22/29</t>
@@ -15164,11 +14124,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G303" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G303" s="2" t="inlineStr"/>
       <c r="H303" s="2" t="inlineStr">
         <is>
           <t>18/29</t>
@@ -15211,11 +14167,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G304" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G304" s="2" t="inlineStr"/>
       <c r="H304" s="2" t="inlineStr">
         <is>
           <t>22/29</t>
@@ -15258,11 +14210,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G305" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G305" s="2" t="inlineStr"/>
       <c r="H305" s="2" t="inlineStr">
         <is>
           <t>22/29</t>
@@ -15305,11 +14253,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G306" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G306" s="2" t="inlineStr"/>
       <c r="H306" s="2" t="inlineStr">
         <is>
           <t>22/29</t>
@@ -15352,11 +14296,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G307" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G307" s="2" t="inlineStr"/>
       <c r="H307" s="2" t="inlineStr">
         <is>
           <t>16/29</t>
@@ -15399,11 +14339,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G308" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G308" s="2" t="inlineStr"/>
       <c r="H308" s="2" t="inlineStr">
         <is>
           <t>19/29</t>
@@ -15446,11 +14382,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G309" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G309" s="2" t="inlineStr"/>
       <c r="H309" s="2" t="inlineStr">
         <is>
           <t>25/29</t>
@@ -15493,11 +14425,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G310" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G310" s="2" t="inlineStr"/>
       <c r="H310" s="2" t="inlineStr">
         <is>
           <t>28/29</t>
@@ -15540,11 +14468,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G311" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G311" s="2" t="inlineStr"/>
       <c r="H311" s="2" t="inlineStr">
         <is>
           <t>29/29</t>
@@ -15587,11 +14511,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G312" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr, Administrator</t>
-        </is>
-      </c>
+      <c r="G312" s="2" t="inlineStr"/>
       <c r="H312" s="2" t="inlineStr">
         <is>
           <t>29/29</t>
@@ -15634,11 +14554,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G313" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G313" s="2" t="inlineStr"/>
       <c r="H313" s="2" t="inlineStr">
         <is>
           <t>18/29</t>
@@ -15681,11 +14597,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G314" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G314" s="2" t="inlineStr"/>
       <c r="H314" s="2" t="inlineStr">
         <is>
           <t>21/29</t>
@@ -15728,11 +14640,7 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G315" s="2" t="inlineStr">
-        <is>
-          <t>Miss Dina Nasr</t>
-        </is>
-      </c>
+      <c r="G315" s="2" t="inlineStr"/>
       <c r="H315" s="2" t="inlineStr">
         <is>
           <t>21/29</t>

--- a/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B1_session_analysis.xlsx
+++ b/attendance_reports/Y4_B2526_General_&_Special_Surgery_1_B1_session_analysis.xlsx
@@ -479,7 +479,7 @@
     <col width="9" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="31" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="22" customWidth="1" min="11" max="11"/>
@@ -571,7 +571,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr"/>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
           <t>10/26</t>
@@ -672,7 +676,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr"/>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
           <t>22/26</t>
@@ -723,7 +731,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr"/>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
           <t>26/26</t>
@@ -774,7 +786,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr"/>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
           <t>22/26</t>
@@ -825,7 +841,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr"/>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
           <t>20/26</t>
@@ -876,7 +896,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr"/>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
           <t>26/26</t>
@@ -927,7 +951,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr"/>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
           <t>21/26</t>
@@ -980,7 +1008,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr"/>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
           <t>20/26</t>
@@ -1033,7 +1065,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr"/>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
           <t>24/26</t>
@@ -1076,7 +1112,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr"/>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
           <t>19/26</t>
@@ -1119,7 +1159,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr"/>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
           <t>24/26</t>
@@ -1167,7 +1211,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr"/>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
           <t>25/26</t>
@@ -1255,7 +1303,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr"/>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
           <t>22/26</t>
@@ -1333,7 +1385,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr"/>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
           <t>22/26</t>
@@ -1411,7 +1467,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr"/>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
           <t>18/26</t>
@@ -1489,7 +1549,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr"/>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
           <t>22/26</t>
@@ -1567,7 +1631,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr"/>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
           <t>19/26</t>
@@ -1645,7 +1713,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr"/>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
           <t>20/26</t>
@@ -1723,7 +1795,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr"/>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
           <t>26/26</t>
@@ -1801,7 +1877,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr"/>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
           <t>18/26</t>
@@ -1879,7 +1959,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr"/>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
           <t>20/26</t>
@@ -1957,7 +2041,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr"/>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
           <t>16/26</t>
@@ -2234,7 +2322,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr"/>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
           <t>17/27</t>
@@ -2277,7 +2369,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr"/>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
           <t>1/27</t>
@@ -2325,7 +2421,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr"/>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
           <t>20/27</t>
@@ -2383,7 +2483,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr"/>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
           <t>27/27</t>
@@ -2441,7 +2545,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr"/>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
           <t>24/27</t>
@@ -2499,7 +2607,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr"/>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
           <t>21/27</t>
@@ -2557,7 +2669,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr"/>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
           <t>25/27</t>
@@ -2600,7 +2716,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr"/>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
           <t>24/27</t>
@@ -2643,7 +2763,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr"/>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
           <t>23/27</t>
@@ -2686,7 +2810,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr"/>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
           <t>22/27</t>
@@ -2729,7 +2857,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr"/>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
           <t>26/27</t>
@@ -2772,7 +2904,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr"/>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
           <t>24/27</t>
@@ -2815,7 +2951,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr"/>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
           <t>26/27</t>
@@ -2858,7 +2998,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr"/>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
           <t>24/27</t>
@@ -2901,7 +3045,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr"/>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
           <t>24/27</t>
@@ -2944,7 +3092,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr"/>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
           <t>22/27</t>
@@ -2987,7 +3139,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr"/>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
           <t>24/27</t>
@@ -3030,7 +3186,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr"/>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
           <t>20/27</t>
@@ -3073,7 +3233,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr"/>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
           <t>20/27</t>
@@ -3116,7 +3280,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr"/>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
           <t>27/27</t>
@@ -3159,7 +3327,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr"/>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
           <t>23/27</t>
@@ -3202,7 +3374,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr"/>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
           <t>23/27</t>
@@ -3245,7 +3421,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr"/>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
           <t>17/27</t>
@@ -3417,7 +3597,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr"/>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
           <t>13/26</t>
@@ -3460,7 +3644,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr"/>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
           <t>20/26</t>
@@ -3503,7 +3691,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr"/>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
           <t>1/26</t>
@@ -3546,7 +3738,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr"/>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
           <t>25/26</t>
@@ -3589,7 +3785,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr"/>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
           <t>19/26</t>
@@ -3632,7 +3832,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr"/>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
           <t>21/26</t>
@@ -3675,7 +3879,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr"/>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
           <t>25/26</t>
@@ -3718,7 +3926,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G61" s="2" t="inlineStr"/>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
           <t>20/26</t>
@@ -3761,7 +3973,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr"/>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
           <t>19/26</t>
@@ -3804,7 +4020,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G63" s="2" t="inlineStr"/>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
           <t>16/26</t>
@@ -3847,7 +4067,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr"/>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
           <t>17/26</t>
@@ -3890,7 +4114,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr"/>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
           <t>20/26</t>
@@ -3933,7 +4161,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr"/>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
           <t>22/26</t>
@@ -3976,7 +4208,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr"/>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
           <t>19/26</t>
@@ -4019,7 +4255,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr"/>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
           <t>21/26</t>
@@ -4062,7 +4302,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G69" s="2" t="inlineStr"/>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
           <t>19/26</t>
@@ -4105,7 +4349,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G70" s="2" t="inlineStr"/>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
           <t>18/26</t>
@@ -4148,7 +4396,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G71" s="2" t="inlineStr"/>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
           <t>17/26</t>
@@ -4191,7 +4443,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G72" s="2" t="inlineStr"/>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
           <t>18/26</t>
@@ -4234,7 +4490,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G73" s="2" t="inlineStr"/>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
           <t>26/26</t>
@@ -4277,7 +4537,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G74" s="2" t="inlineStr"/>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
           <t>23/26</t>
@@ -4320,7 +4584,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G75" s="2" t="inlineStr"/>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
           <t>21/26</t>
@@ -4363,7 +4631,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G76" s="2" t="inlineStr"/>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
           <t>21/26</t>
@@ -4535,7 +4807,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G80" s="2" t="inlineStr"/>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
           <t>10/27</t>
@@ -4578,7 +4854,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G81" s="2" t="inlineStr"/>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
           <t>21/27</t>
@@ -4621,7 +4901,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G82" s="2" t="inlineStr"/>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
           <t>2/27</t>
@@ -4664,7 +4948,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G83" s="2" t="inlineStr"/>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
           <t>25/27</t>
@@ -4707,7 +4995,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G84" s="2" t="inlineStr"/>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
           <t>22/27</t>
@@ -4750,7 +5042,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G85" s="2" t="inlineStr"/>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
           <t>23/27</t>
@@ -4793,7 +5089,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G86" s="2" t="inlineStr"/>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
           <t>24/27</t>
@@ -4836,7 +5136,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G87" s="2" t="inlineStr"/>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
           <t>22/27</t>
@@ -4879,7 +5183,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G88" s="2" t="inlineStr"/>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
           <t>19/27</t>
@@ -4922,7 +5230,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G89" s="2" t="inlineStr"/>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
           <t>24/27</t>
@@ -4965,7 +5277,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G90" s="2" t="inlineStr"/>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
           <t>23/27</t>
@@ -5008,7 +5324,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G91" s="2" t="inlineStr"/>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
           <t>23/27</t>
@@ -5051,7 +5371,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G92" s="2" t="inlineStr"/>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
           <t>26/27</t>
@@ -5094,7 +5418,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G93" s="2" t="inlineStr"/>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
           <t>21/27</t>
@@ -5137,7 +5465,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G94" s="2" t="inlineStr"/>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
           <t>21/27</t>
@@ -5180,7 +5512,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G95" s="2" t="inlineStr"/>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
           <t>24/27</t>
@@ -5223,7 +5559,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G96" s="2" t="inlineStr"/>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
           <t>20/27</t>
@@ -5266,7 +5606,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G97" s="2" t="inlineStr"/>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
           <t>24/27</t>
@@ -5309,7 +5653,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G98" s="2" t="inlineStr"/>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
           <t>27/27</t>
@@ -5352,7 +5700,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G99" s="2" t="inlineStr"/>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
           <t>27/27</t>
@@ -5395,7 +5747,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G100" s="2" t="inlineStr"/>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
           <t>24/27</t>
@@ -5438,7 +5794,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G101" s="2" t="inlineStr"/>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
           <t>18/27</t>
@@ -5481,7 +5841,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G102" s="2" t="inlineStr"/>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
           <t>16/27</t>
@@ -5653,7 +6017,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G106" s="2" t="inlineStr"/>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
           <t>2/30</t>
@@ -5696,7 +6064,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G107" s="2" t="inlineStr"/>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
           <t>14/30</t>
@@ -5739,7 +6111,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G108" s="2" t="inlineStr"/>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
           <t>16/30</t>
@@ -5782,7 +6158,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G109" s="2" t="inlineStr"/>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
           <t>30/30</t>
@@ -5825,7 +6205,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G110" s="2" t="inlineStr"/>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
           <t>23/30</t>
@@ -5868,7 +6252,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G111" s="2" t="inlineStr"/>
+      <c r="G111" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
           <t>26/30</t>
@@ -5911,7 +6299,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G112" s="2" t="inlineStr"/>
+      <c r="G112" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
           <t>26/30</t>
@@ -5954,7 +6346,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G113" s="2" t="inlineStr"/>
+      <c r="G113" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
           <t>27/30</t>
@@ -5997,7 +6393,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G114" s="2" t="inlineStr"/>
+      <c r="G114" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
           <t>25/30</t>
@@ -6040,7 +6440,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G115" s="2" t="inlineStr"/>
+      <c r="G115" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
           <t>22/30</t>
@@ -6083,7 +6487,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G116" s="2" t="inlineStr"/>
+      <c r="G116" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
           <t>24/30</t>
@@ -6126,7 +6534,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G117" s="2" t="inlineStr"/>
+      <c r="G117" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
           <t>26/30</t>
@@ -6169,7 +6581,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G118" s="2" t="inlineStr"/>
+      <c r="G118" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
           <t>28/30</t>
@@ -6212,7 +6628,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G119" s="2" t="inlineStr"/>
+      <c r="G119" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
           <t>29/30</t>
@@ -6255,7 +6675,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G120" s="2" t="inlineStr"/>
+      <c r="G120" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
           <t>22/30</t>
@@ -6298,7 +6722,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G121" s="2" t="inlineStr"/>
+      <c r="G121" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
           <t>26/30</t>
@@ -6341,7 +6769,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G122" s="2" t="inlineStr"/>
+      <c r="G122" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
           <t>22/30</t>
@@ -6384,7 +6816,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G123" s="2" t="inlineStr"/>
+      <c r="G123" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H123" s="2" t="inlineStr">
         <is>
           <t>25/30</t>
@@ -6427,7 +6863,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G124" s="2" t="inlineStr"/>
+      <c r="G124" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
           <t>25/30</t>
@@ -6470,7 +6910,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G125" s="2" t="inlineStr"/>
+      <c r="G125" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H125" s="2" t="inlineStr">
         <is>
           <t>30/30</t>
@@ -6513,7 +6957,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G126" s="2" t="inlineStr"/>
+      <c r="G126" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
           <t>26/30</t>
@@ -6556,7 +7004,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G127" s="2" t="inlineStr"/>
+      <c r="G127" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H127" s="2" t="inlineStr">
         <is>
           <t>23/30</t>
@@ -6599,7 +7051,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G128" s="2" t="inlineStr"/>
+      <c r="G128" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H128" s="2" t="inlineStr">
         <is>
           <t>21/30</t>
@@ -6814,7 +7270,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G133" s="2" t="inlineStr"/>
+      <c r="G133" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H133" s="2" t="inlineStr">
         <is>
           <t>12/23</t>
@@ -6857,7 +7317,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G134" s="2" t="inlineStr"/>
+      <c r="G134" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H134" s="2" t="inlineStr">
         <is>
           <t>17/23</t>
@@ -6900,7 +7364,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G135" s="2" t="inlineStr"/>
+      <c r="G135" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H135" s="2" t="inlineStr">
         <is>
           <t>23/23</t>
@@ -6943,7 +7411,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G136" s="2" t="inlineStr"/>
+      <c r="G136" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
           <t>18/23</t>
@@ -6986,7 +7458,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G137" s="2" t="inlineStr"/>
+      <c r="G137" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H137" s="2" t="inlineStr">
         <is>
           <t>15/23</t>
@@ -7029,7 +7505,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G138" s="2" t="inlineStr"/>
+      <c r="G138" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H138" s="2" t="inlineStr">
         <is>
           <t>21/23</t>
@@ -7072,7 +7552,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G139" s="2" t="inlineStr"/>
+      <c r="G139" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H139" s="2" t="inlineStr">
         <is>
           <t>16/23</t>
@@ -7115,7 +7599,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G140" s="2" t="inlineStr"/>
+      <c r="G140" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H140" s="2" t="inlineStr">
         <is>
           <t>19/23</t>
@@ -7158,7 +7646,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G141" s="2" t="inlineStr"/>
+      <c r="G141" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H141" s="2" t="inlineStr">
         <is>
           <t>20/23</t>
@@ -7201,7 +7693,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G142" s="2" t="inlineStr"/>
+      <c r="G142" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H142" s="2" t="inlineStr">
         <is>
           <t>17/23</t>
@@ -7244,7 +7740,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G143" s="2" t="inlineStr"/>
+      <c r="G143" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H143" s="2" t="inlineStr">
         <is>
           <t>20/23</t>
@@ -7287,7 +7787,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G144" s="2" t="inlineStr"/>
+      <c r="G144" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H144" s="2" t="inlineStr">
         <is>
           <t>23/23</t>
@@ -7330,7 +7834,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G145" s="2" t="inlineStr"/>
+      <c r="G145" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H145" s="2" t="inlineStr">
         <is>
           <t>18/23</t>
@@ -7373,7 +7881,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G146" s="2" t="inlineStr"/>
+      <c r="G146" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H146" s="2" t="inlineStr">
         <is>
           <t>18/23</t>
@@ -7416,7 +7928,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G147" s="2" t="inlineStr"/>
+      <c r="G147" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H147" s="2" t="inlineStr">
         <is>
           <t>21/23</t>
@@ -7459,7 +7975,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G148" s="2" t="inlineStr"/>
+      <c r="G148" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H148" s="2" t="inlineStr">
         <is>
           <t>18/23</t>
@@ -7502,7 +8022,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G149" s="2" t="inlineStr"/>
+      <c r="G149" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H149" s="2" t="inlineStr">
         <is>
           <t>17/23</t>
@@ -7545,7 +8069,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G150" s="2" t="inlineStr"/>
+      <c r="G150" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H150" s="2" t="inlineStr">
         <is>
           <t>18/23</t>
@@ -7588,7 +8116,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G151" s="2" t="inlineStr"/>
+      <c r="G151" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H151" s="2" t="inlineStr">
         <is>
           <t>23/23</t>
@@ -7631,7 +8163,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G152" s="2" t="inlineStr"/>
+      <c r="G152" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H152" s="2" t="inlineStr">
         <is>
           <t>18/23</t>
@@ -7674,7 +8210,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G153" s="2" t="inlineStr"/>
+      <c r="G153" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H153" s="2" t="inlineStr">
         <is>
           <t>16/23</t>
@@ -7717,7 +8257,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G154" s="2" t="inlineStr"/>
+      <c r="G154" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H154" s="2" t="inlineStr">
         <is>
           <t>17/23</t>
@@ -7889,7 +8433,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G158" s="2" t="inlineStr"/>
+      <c r="G158" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H158" s="2" t="inlineStr">
         <is>
           <t>18/23</t>
@@ -7932,7 +8480,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G159" s="2" t="inlineStr"/>
+      <c r="G159" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H159" s="2" t="inlineStr">
         <is>
           <t>1/23</t>
@@ -7975,7 +8527,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G160" s="2" t="inlineStr"/>
+      <c r="G160" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H160" s="2" t="inlineStr">
         <is>
           <t>18/23</t>
@@ -8018,7 +8574,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G161" s="2" t="inlineStr"/>
+      <c r="G161" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H161" s="2" t="inlineStr">
         <is>
           <t>21/23</t>
@@ -8061,7 +8621,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G162" s="2" t="inlineStr"/>
+      <c r="G162" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H162" s="2" t="inlineStr">
         <is>
           <t>18/23</t>
@@ -8104,7 +8668,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G163" s="2" t="inlineStr"/>
+      <c r="G163" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H163" s="2" t="inlineStr">
         <is>
           <t>22/23</t>
@@ -8147,7 +8715,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G164" s="2" t="inlineStr"/>
+      <c r="G164" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H164" s="2" t="inlineStr">
         <is>
           <t>22/23</t>
@@ -8190,7 +8762,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G165" s="2" t="inlineStr"/>
+      <c r="G165" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H165" s="2" t="inlineStr">
         <is>
           <t>14/23</t>
@@ -8233,7 +8809,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G166" s="2" t="inlineStr"/>
+      <c r="G166" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H166" s="2" t="inlineStr">
         <is>
           <t>20/23</t>
@@ -8276,7 +8856,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G167" s="2" t="inlineStr"/>
+      <c r="G167" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H167" s="2" t="inlineStr">
         <is>
           <t>22/23</t>
@@ -8319,7 +8903,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G168" s="2" t="inlineStr"/>
+      <c r="G168" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H168" s="2" t="inlineStr">
         <is>
           <t>19/23</t>
@@ -8362,7 +8950,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G169" s="2" t="inlineStr"/>
+      <c r="G169" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H169" s="2" t="inlineStr">
         <is>
           <t>19/23</t>
@@ -8405,7 +8997,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G170" s="2" t="inlineStr"/>
+      <c r="G170" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H170" s="2" t="inlineStr">
         <is>
           <t>16/23</t>
@@ -8448,7 +9044,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G171" s="2" t="inlineStr"/>
+      <c r="G171" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H171" s="2" t="inlineStr">
         <is>
           <t>20/23</t>
@@ -8491,7 +9091,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G172" s="2" t="inlineStr"/>
+      <c r="G172" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H172" s="2" t="inlineStr">
         <is>
           <t>19/23</t>
@@ -8534,7 +9138,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G173" s="2" t="inlineStr"/>
+      <c r="G173" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H173" s="2" t="inlineStr">
         <is>
           <t>18/23</t>
@@ -8577,7 +9185,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G174" s="2" t="inlineStr"/>
+      <c r="G174" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H174" s="2" t="inlineStr">
         <is>
           <t>19/23</t>
@@ -8620,7 +9232,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G175" s="2" t="inlineStr"/>
+      <c r="G175" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H175" s="2" t="inlineStr">
         <is>
           <t>22/23</t>
@@ -8663,7 +9279,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G176" s="2" t="inlineStr"/>
+      <c r="G176" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H176" s="2" t="inlineStr">
         <is>
           <t>23/23</t>
@@ -8706,7 +9326,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G177" s="2" t="inlineStr"/>
+      <c r="G177" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H177" s="2" t="inlineStr">
         <is>
           <t>23/23</t>
@@ -8749,7 +9373,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G178" s="2" t="inlineStr"/>
+      <c r="G178" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H178" s="2" t="inlineStr">
         <is>
           <t>17/23</t>
@@ -8792,7 +9420,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G179" s="2" t="inlineStr"/>
+      <c r="G179" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H179" s="2" t="inlineStr">
         <is>
           <t>20/23</t>
@@ -8835,7 +9467,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G180" s="2" t="inlineStr"/>
+      <c r="G180" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H180" s="2" t="inlineStr">
         <is>
           <t>19/23</t>
@@ -9050,7 +9686,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G185" s="2" t="inlineStr"/>
+      <c r="G185" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H185" s="2" t="inlineStr">
         <is>
           <t>23/30</t>
@@ -9093,7 +9733,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G186" s="2" t="inlineStr"/>
+      <c r="G186" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H186" s="2" t="inlineStr">
         <is>
           <t>2/30</t>
@@ -9136,7 +9780,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G187" s="2" t="inlineStr"/>
+      <c r="G187" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H187" s="2" t="inlineStr">
         <is>
           <t>23/30</t>
@@ -9179,7 +9827,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G188" s="2" t="inlineStr"/>
+      <c r="G188" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H188" s="2" t="inlineStr">
         <is>
           <t>23/30</t>
@@ -9222,7 +9874,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G189" s="2" t="inlineStr"/>
+      <c r="G189" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H189" s="2" t="inlineStr">
         <is>
           <t>27/30</t>
@@ -9265,7 +9921,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G190" s="2" t="inlineStr"/>
+      <c r="G190" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H190" s="2" t="inlineStr">
         <is>
           <t>26/30</t>
@@ -9308,7 +9968,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G191" s="2" t="inlineStr"/>
+      <c r="G191" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H191" s="2" t="inlineStr">
         <is>
           <t>23/30</t>
@@ -9351,7 +10015,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G192" s="2" t="inlineStr"/>
+      <c r="G192" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H192" s="2" t="inlineStr">
         <is>
           <t>24/30</t>
@@ -9394,7 +10062,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G193" s="2" t="inlineStr"/>
+      <c r="G193" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H193" s="2" t="inlineStr">
         <is>
           <t>24/30</t>
@@ -9437,7 +10109,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G194" s="2" t="inlineStr"/>
+      <c r="G194" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H194" s="2" t="inlineStr">
         <is>
           <t>26/30</t>
@@ -9480,7 +10156,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G195" s="2" t="inlineStr"/>
+      <c r="G195" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H195" s="2" t="inlineStr">
         <is>
           <t>24/30</t>
@@ -9523,7 +10203,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G196" s="2" t="inlineStr"/>
+      <c r="G196" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H196" s="2" t="inlineStr">
         <is>
           <t>27/30</t>
@@ -9566,7 +10250,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G197" s="2" t="inlineStr"/>
+      <c r="G197" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H197" s="2" t="inlineStr">
         <is>
           <t>25/30</t>
@@ -9609,7 +10297,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G198" s="2" t="inlineStr"/>
+      <c r="G198" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H198" s="2" t="inlineStr">
         <is>
           <t>22/30</t>
@@ -9652,7 +10344,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G199" s="2" t="inlineStr"/>
+      <c r="G199" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H199" s="2" t="inlineStr">
         <is>
           <t>26/30</t>
@@ -9695,7 +10391,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G200" s="2" t="inlineStr"/>
+      <c r="G200" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H200" s="2" t="inlineStr">
         <is>
           <t>27/30</t>
@@ -9738,7 +10438,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G201" s="2" t="inlineStr"/>
+      <c r="G201" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H201" s="2" t="inlineStr">
         <is>
           <t>21/30</t>
@@ -9781,7 +10485,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G202" s="2" t="inlineStr"/>
+      <c r="G202" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H202" s="2" t="inlineStr">
         <is>
           <t>27/30</t>
@@ -9824,7 +10532,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G203" s="2" t="inlineStr"/>
+      <c r="G203" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H203" s="2" t="inlineStr">
         <is>
           <t>30/30</t>
@@ -9867,7 +10579,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G204" s="2" t="inlineStr"/>
+      <c r="G204" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H204" s="2" t="inlineStr">
         <is>
           <t>30/30</t>
@@ -9910,7 +10626,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G205" s="2" t="inlineStr"/>
+      <c r="G205" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H205" s="2" t="inlineStr">
         <is>
           <t>26/30</t>
@@ -9953,7 +10673,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G206" s="2" t="inlineStr"/>
+      <c r="G206" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H206" s="2" t="inlineStr">
         <is>
           <t>23/30</t>
@@ -9996,7 +10720,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G207" s="2" t="inlineStr"/>
+      <c r="G207" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H207" s="2" t="inlineStr">
         <is>
           <t>22/30</t>
@@ -10211,7 +10939,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G212" s="2" t="inlineStr"/>
+      <c r="G212" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H212" s="2" t="inlineStr">
         <is>
           <t>20/26</t>
@@ -10254,7 +10986,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G213" s="2" t="inlineStr"/>
+      <c r="G213" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H213" s="2" t="inlineStr">
         <is>
           <t>19/26</t>
@@ -10297,7 +11033,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G214" s="2" t="inlineStr"/>
+      <c r="G214" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H214" s="2" t="inlineStr">
         <is>
           <t>3/26</t>
@@ -10340,7 +11080,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G215" s="2" t="inlineStr"/>
+      <c r="G215" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H215" s="2" t="inlineStr">
         <is>
           <t>24/26</t>
@@ -10383,7 +11127,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G216" s="2" t="inlineStr"/>
+      <c r="G216" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H216" s="2" t="inlineStr">
         <is>
           <t>20/26</t>
@@ -10426,7 +11174,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G217" s="2" t="inlineStr"/>
+      <c r="G217" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H217" s="2" t="inlineStr">
         <is>
           <t>24/26</t>
@@ -10469,7 +11221,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G218" s="2" t="inlineStr"/>
+      <c r="G218" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H218" s="2" t="inlineStr">
         <is>
           <t>26/26</t>
@@ -10512,7 +11268,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G219" s="2" t="inlineStr"/>
+      <c r="G219" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H219" s="2" t="inlineStr">
         <is>
           <t>24/26</t>
@@ -10555,7 +11315,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G220" s="2" t="inlineStr"/>
+      <c r="G220" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H220" s="2" t="inlineStr">
         <is>
           <t>25/26</t>
@@ -10598,7 +11362,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G221" s="2" t="inlineStr"/>
+      <c r="G221" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H221" s="2" t="inlineStr">
         <is>
           <t>25/26</t>
@@ -10641,7 +11409,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G222" s="2" t="inlineStr"/>
+      <c r="G222" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H222" s="2" t="inlineStr">
         <is>
           <t>21/26</t>
@@ -10684,7 +11456,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G223" s="2" t="inlineStr"/>
+      <c r="G223" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H223" s="2" t="inlineStr">
         <is>
           <t>22/26</t>
@@ -10727,7 +11503,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G224" s="2" t="inlineStr"/>
+      <c r="G224" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H224" s="2" t="inlineStr">
         <is>
           <t>22/26</t>
@@ -10770,7 +11550,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G225" s="2" t="inlineStr"/>
+      <c r="G225" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H225" s="2" t="inlineStr">
         <is>
           <t>20/26</t>
@@ -10813,7 +11597,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G226" s="2" t="inlineStr"/>
+      <c r="G226" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H226" s="2" t="inlineStr">
         <is>
           <t>18/26</t>
@@ -10856,7 +11644,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G227" s="2" t="inlineStr"/>
+      <c r="G227" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H227" s="2" t="inlineStr">
         <is>
           <t>21/26</t>
@@ -10899,7 +11691,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G228" s="2" t="inlineStr"/>
+      <c r="G228" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H228" s="2" t="inlineStr">
         <is>
           <t>19/26</t>
@@ -10942,7 +11738,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G229" s="2" t="inlineStr"/>
+      <c r="G229" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H229" s="2" t="inlineStr">
         <is>
           <t>22/26</t>
@@ -10985,7 +11785,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G230" s="2" t="inlineStr"/>
+      <c r="G230" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H230" s="2" t="inlineStr">
         <is>
           <t>26/26</t>
@@ -11028,7 +11832,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G231" s="2" t="inlineStr"/>
+      <c r="G231" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H231" s="2" t="inlineStr">
         <is>
           <t>26/26</t>
@@ -11071,7 +11879,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G232" s="2" t="inlineStr"/>
+      <c r="G232" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H232" s="2" t="inlineStr">
         <is>
           <t>14/26</t>
@@ -11114,7 +11926,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G233" s="2" t="inlineStr"/>
+      <c r="G233" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H233" s="2" t="inlineStr">
         <is>
           <t>21/26</t>
@@ -11157,7 +11973,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G234" s="2" t="inlineStr"/>
+      <c r="G234" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H234" s="2" t="inlineStr">
         <is>
           <t>17/26</t>
@@ -11372,7 +12192,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G239" s="2" t="inlineStr"/>
+      <c r="G239" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H239" s="2" t="inlineStr">
         <is>
           <t>17/28</t>
@@ -11415,7 +12239,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G240" s="2" t="inlineStr"/>
+      <c r="G240" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H240" s="2" t="inlineStr">
         <is>
           <t>17/28</t>
@@ -11501,7 +12329,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G242" s="2" t="inlineStr"/>
+      <c r="G242" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H242" s="2" t="inlineStr">
         <is>
           <t>18/28</t>
@@ -11544,7 +12376,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G243" s="2" t="inlineStr"/>
+      <c r="G243" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H243" s="2" t="inlineStr">
         <is>
           <t>14/28</t>
@@ -11587,7 +12423,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G244" s="2" t="inlineStr"/>
+      <c r="G244" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H244" s="2" t="inlineStr">
         <is>
           <t>21/28</t>
@@ -11630,7 +12470,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G245" s="2" t="inlineStr"/>
+      <c r="G245" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H245" s="2" t="inlineStr">
         <is>
           <t>26/28</t>
@@ -11673,7 +12517,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G246" s="2" t="inlineStr"/>
+      <c r="G246" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H246" s="2" t="inlineStr">
         <is>
           <t>16/28</t>
@@ -11716,7 +12564,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G247" s="2" t="inlineStr"/>
+      <c r="G247" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H247" s="2" t="inlineStr">
         <is>
           <t>19/28</t>
@@ -11759,7 +12611,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G248" s="2" t="inlineStr"/>
+      <c r="G248" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H248" s="2" t="inlineStr">
         <is>
           <t>23/28</t>
@@ -11802,7 +12658,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G249" s="2" t="inlineStr"/>
+      <c r="G249" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H249" s="2" t="inlineStr">
         <is>
           <t>25/28</t>
@@ -11845,7 +12705,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G250" s="2" t="inlineStr"/>
+      <c r="G250" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H250" s="2" t="inlineStr">
         <is>
           <t>21/28</t>
@@ -11888,7 +12752,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G251" s="2" t="inlineStr"/>
+      <c r="G251" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H251" s="2" t="inlineStr">
         <is>
           <t>21/28</t>
@@ -11931,7 +12799,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G252" s="2" t="inlineStr"/>
+      <c r="G252" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H252" s="2" t="inlineStr">
         <is>
           <t>20/28</t>
@@ -11974,7 +12846,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G253" s="2" t="inlineStr"/>
+      <c r="G253" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H253" s="2" t="inlineStr">
         <is>
           <t>21/28</t>
@@ -12017,7 +12893,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G254" s="2" t="inlineStr"/>
+      <c r="G254" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H254" s="2" t="inlineStr">
         <is>
           <t>22/28</t>
@@ -12060,7 +12940,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G255" s="2" t="inlineStr"/>
+      <c r="G255" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H255" s="2" t="inlineStr">
         <is>
           <t>24/28</t>
@@ -12103,7 +12987,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G256" s="2" t="inlineStr"/>
+      <c r="G256" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H256" s="2" t="inlineStr">
         <is>
           <t>25/28</t>
@@ -12146,7 +13034,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G257" s="2" t="inlineStr"/>
+      <c r="G257" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H257" s="2" t="inlineStr">
         <is>
           <t>28/28</t>
@@ -12189,7 +13081,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G258" s="2" t="inlineStr"/>
+      <c r="G258" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H258" s="2" t="inlineStr">
         <is>
           <t>28/28</t>
@@ -12232,7 +13128,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G259" s="2" t="inlineStr"/>
+      <c r="G259" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H259" s="2" t="inlineStr">
         <is>
           <t>21/28</t>
@@ -12275,7 +13175,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G260" s="2" t="inlineStr"/>
+      <c r="G260" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H260" s="2" t="inlineStr">
         <is>
           <t>16/28</t>
@@ -12318,7 +13222,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G261" s="2" t="inlineStr"/>
+      <c r="G261" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H261" s="2" t="inlineStr">
         <is>
           <t>21/28</t>
@@ -12533,7 +13441,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G266" s="2" t="inlineStr"/>
+      <c r="G266" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H266" s="2" t="inlineStr">
         <is>
           <t>2/26</t>
@@ -12576,7 +13488,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G267" s="2" t="inlineStr"/>
+      <c r="G267" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H267" s="2" t="inlineStr">
         <is>
           <t>18/26</t>
@@ -12619,7 +13535,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G268" s="2" t="inlineStr"/>
+      <c r="G268" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H268" s="2" t="inlineStr">
         <is>
           <t>15/26</t>
@@ -12662,7 +13582,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G269" s="2" t="inlineStr"/>
+      <c r="G269" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H269" s="2" t="inlineStr">
         <is>
           <t>21/26</t>
@@ -12705,7 +13629,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G270" s="2" t="inlineStr"/>
+      <c r="G270" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H270" s="2" t="inlineStr">
         <is>
           <t>21/26</t>
@@ -12748,7 +13676,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G271" s="2" t="inlineStr"/>
+      <c r="G271" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H271" s="2" t="inlineStr">
         <is>
           <t>18/26</t>
@@ -12791,7 +13723,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G272" s="2" t="inlineStr"/>
+      <c r="G272" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H272" s="2" t="inlineStr">
         <is>
           <t>21/26</t>
@@ -12834,7 +13770,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G273" s="2" t="inlineStr"/>
+      <c r="G273" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H273" s="2" t="inlineStr">
         <is>
           <t>20/26</t>
@@ -12877,7 +13817,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G274" s="2" t="inlineStr"/>
+      <c r="G274" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H274" s="2" t="inlineStr">
         <is>
           <t>17/26</t>
@@ -12920,7 +13864,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G275" s="2" t="inlineStr"/>
+      <c r="G275" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H275" s="2" t="inlineStr">
         <is>
           <t>20/26</t>
@@ -12963,7 +13911,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G276" s="2" t="inlineStr"/>
+      <c r="G276" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H276" s="2" t="inlineStr">
         <is>
           <t>20/26</t>
@@ -13006,7 +13958,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G277" s="2" t="inlineStr"/>
+      <c r="G277" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H277" s="2" t="inlineStr">
         <is>
           <t>23/26</t>
@@ -13049,7 +14005,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G278" s="2" t="inlineStr"/>
+      <c r="G278" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H278" s="2" t="inlineStr">
         <is>
           <t>21/26</t>
@@ -13092,7 +14052,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G279" s="2" t="inlineStr"/>
+      <c r="G279" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H279" s="2" t="inlineStr">
         <is>
           <t>15/26</t>
@@ -13135,7 +14099,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G280" s="2" t="inlineStr"/>
+      <c r="G280" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H280" s="2" t="inlineStr">
         <is>
           <t>22/26</t>
@@ -13178,7 +14146,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G281" s="2" t="inlineStr"/>
+      <c r="G281" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H281" s="2" t="inlineStr">
         <is>
           <t>19/26</t>
@@ -13221,7 +14193,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G282" s="2" t="inlineStr"/>
+      <c r="G282" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H282" s="2" t="inlineStr">
         <is>
           <t>20/26</t>
@@ -13264,7 +14240,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G283" s="2" t="inlineStr"/>
+      <c r="G283" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H283" s="2" t="inlineStr">
         <is>
           <t>22/26</t>
@@ -13307,7 +14287,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G284" s="2" t="inlineStr"/>
+      <c r="G284" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H284" s="2" t="inlineStr">
         <is>
           <t>26/26</t>
@@ -13350,7 +14334,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G285" s="2" t="inlineStr"/>
+      <c r="G285" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H285" s="2" t="inlineStr">
         <is>
           <t>26/26</t>
@@ -13393,7 +14381,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G286" s="2" t="inlineStr"/>
+      <c r="G286" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H286" s="2" t="inlineStr">
         <is>
           <t>21/26</t>
@@ -13436,7 +14428,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G287" s="2" t="inlineStr"/>
+      <c r="G287" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H287" s="2" t="inlineStr">
         <is>
           <t>18/26</t>
@@ -13479,7 +14475,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G288" s="2" t="inlineStr"/>
+      <c r="G288" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H288" s="2" t="inlineStr">
         <is>
           <t>20/26</t>
@@ -13694,7 +14694,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G293" s="2" t="inlineStr"/>
+      <c r="G293" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H293" s="2" t="inlineStr">
         <is>
           <t>1/29</t>
@@ -13737,7 +14741,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G294" s="2" t="inlineStr"/>
+      <c r="G294" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H294" s="2" t="inlineStr">
         <is>
           <t>20/29</t>
@@ -13780,7 +14788,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G295" s="2" t="inlineStr"/>
+      <c r="G295" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H295" s="2" t="inlineStr">
         <is>
           <t>15/29</t>
@@ -13823,7 +14835,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G296" s="2" t="inlineStr"/>
+      <c r="G296" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H296" s="2" t="inlineStr">
         <is>
           <t>21/29</t>
@@ -13866,7 +14882,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G297" s="2" t="inlineStr"/>
+      <c r="G297" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H297" s="2" t="inlineStr">
         <is>
           <t>21/29</t>
@@ -13909,7 +14929,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G298" s="2" t="inlineStr"/>
+      <c r="G298" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H298" s="2" t="inlineStr">
         <is>
           <t>15/29</t>
@@ -13952,7 +14976,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G299" s="2" t="inlineStr"/>
+      <c r="G299" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H299" s="2" t="inlineStr">
         <is>
           <t>20/29</t>
@@ -13995,7 +15023,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G300" s="2" t="inlineStr"/>
+      <c r="G300" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H300" s="2" t="inlineStr">
         <is>
           <t>22/29</t>
@@ -14038,7 +15070,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G301" s="2" t="inlineStr"/>
+      <c r="G301" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H301" s="2" t="inlineStr">
         <is>
           <t>14/29</t>
@@ -14081,7 +15117,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G302" s="2" t="inlineStr"/>
+      <c r="G302" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H302" s="2" t="inlineStr">
         <is>
           <t>22/29</t>
@@ -14124,7 +15164,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G303" s="2" t="inlineStr"/>
+      <c r="G303" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H303" s="2" t="inlineStr">
         <is>
           <t>18/29</t>
@@ -14167,7 +15211,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G304" s="2" t="inlineStr"/>
+      <c r="G304" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H304" s="2" t="inlineStr">
         <is>
           <t>22/29</t>
@@ -14210,7 +15258,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G305" s="2" t="inlineStr"/>
+      <c r="G305" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H305" s="2" t="inlineStr">
         <is>
           <t>22/29</t>
@@ -14253,7 +15305,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G306" s="2" t="inlineStr"/>
+      <c r="G306" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H306" s="2" t="inlineStr">
         <is>
           <t>22/29</t>
@@ -14296,7 +15352,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G307" s="2" t="inlineStr"/>
+      <c r="G307" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H307" s="2" t="inlineStr">
         <is>
           <t>16/29</t>
@@ -14339,7 +15399,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G308" s="2" t="inlineStr"/>
+      <c r="G308" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H308" s="2" t="inlineStr">
         <is>
           <t>19/29</t>
@@ -14382,7 +15446,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G309" s="2" t="inlineStr"/>
+      <c r="G309" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H309" s="2" t="inlineStr">
         <is>
           <t>25/29</t>
@@ -14425,7 +15493,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G310" s="2" t="inlineStr"/>
+      <c r="G310" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H310" s="2" t="inlineStr">
         <is>
           <t>28/29</t>
@@ -14468,7 +15540,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G311" s="2" t="inlineStr"/>
+      <c r="G311" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H311" s="2" t="inlineStr">
         <is>
           <t>29/29</t>
@@ -14511,7 +15587,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G312" s="2" t="inlineStr"/>
+      <c r="G312" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr, Administrator</t>
+        </is>
+      </c>
       <c r="H312" s="2" t="inlineStr">
         <is>
           <t>29/29</t>
@@ -14554,7 +15634,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G313" s="2" t="inlineStr"/>
+      <c r="G313" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H313" s="2" t="inlineStr">
         <is>
           <t>18/29</t>
@@ -14597,7 +15681,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G314" s="2" t="inlineStr"/>
+      <c r="G314" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H314" s="2" t="inlineStr">
         <is>
           <t>21/29</t>
@@ -14640,7 +15728,11 @@
           <t>10:30:00</t>
         </is>
       </c>
-      <c r="G315" s="2" t="inlineStr"/>
+      <c r="G315" s="2" t="inlineStr">
+        <is>
+          <t>Miss Dina Nasr</t>
+        </is>
+      </c>
       <c r="H315" s="2" t="inlineStr">
         <is>
           <t>21/29</t>
